--- a/untitled folder/HSC_Physics_2nd_Paper_Chapter_05_Electromagnetic_Induction_and_Alternating_Current.xlsx
+++ b/untitled folder/HSC_Physics_2nd_Paper_Chapter_05_Electromagnetic_Induction_and_Alternating_Current.xlsx
@@ -1219,11 +1219,6 @@
           <t>$R$ মোট রোধের একটি বদ্ধ কুণ্ডলীর সাথে জড়িত চৌম্বক ফ্লাক্স $\Phi_1$ থেকে পরিবর্তিত হয়ে $\Phi_2$ হলো। প্রমাণ করো যে ফ্লাক্স পরিবর্তনের প্রক্রিয়ার সময়কাল যাই হোক না কেন, কুণ্ডলীর প্রস্থচ্ছেদের মধ্য দিয়ে অতিক্রান্ত মোট আধান কেবল ফ্লাক্সের পার্থক্যের ওপর নির্ভর করে এবং তা $\Delta Q = \frac{\Delta \Phi_B}{R}$।</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>যেকোনো ক্ষণে ফ্যারাডের সূত্রানুযায়ী আবিষ্ট তড়িচ্চালক বল $|\mathcal{E}| = \frac{d\Phi_B}{dt}$। বর্তনীতে ক্ষণিক প্রবাহ $i = \frac{|\mathcal{E}|}{R} = \frac{1}{R}\frac{d\Phi_B}{dt}$। কিন্তু কারেন্টের সংজ্ঞামতে $i = \frac{dq}{dt}$। অতএব $\frac{dq}{dt} = \frac{1}{R}\frac{d\Phi_B}{dt} \implies dq = \frac{d\Phi_B}{R}$। সময়কাল $t_1$ থেকে $t_2$ পর্যন্ত সমগ্র প্রক্রিয়ার জন্য সমাকলন করে পাই: $\Delta Q = \int dq = \frac{1}{R}\int_{\Phi_1}^{\Phi_2} d\Phi_B = \frac{\Phi_2 - \Phi_1}{R} = \frac{\Delta \Phi_B}{R}$। সমীকরণটিতে সময় পদটি সম্পূর্ণরূপে কাটাকাটি হয়ে যায়। ফলে ব্যালাস্টিক গ্যালভানোমিটার দিয়ে এই আধান মেপে অজানা চৌম্বক ফ্লাক্স নিখুঁতভাবে পরিমাপ করা যায়।</t>
@@ -1269,11 +1264,6 @@
           <t>একটি সাধারণ ধাতব কুণ্ডলী এবং একটি শূন্য রোধের সুপারকন্ডাক্টিং কুণ্ডলীর ($R=0$) মধ্য দিয়ে প্রবাহিত চৌম্বক ফ্লাক্স পরিবর্তনের চেষ্টা করা হলো। সুপারকন্ডাক্টিং কুণ্ডলী কেন তার মধ্য দিয়ে চৌম্বক ফ্লাক্সের যেকোনো পরিবর্তনকে শতভাগ প্রতিহত করে ফ্লাক্স ট্র্যাপিং নিশ্চিত করে?</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>একটি সুপারকন্ডাক্টিং রিংয়ের মোট ফ্লাক্স হলো বহিঃস্থ ফ্লাক্স এবং নিজস্ব আবেশিত কারেন্টের ফ্লাক্সের সমষ্টি: $\Phi_{\text{total}} = \Phi_{\text{ext}} + L i$। বর্তনীর সমীকরণ: $\mathcal{E} = -\frac{d\Phi_{\text{total}}}{dt} = i R$। যেহেতু সুপারকন্ডাক্টরের রোধ নিখুঁতভাবে শূন্য ($R = 0$), তাই $-\frac{d\Phi_{\text{total}}}{dt} = 0 \implies \Phi_{\text{total}} = \text{constant}$। এর অর্থ হলো যখনই বহিঃস্থ ক্ষেত্র পরিবর্তনের চেষ্টা করা হয়, রিংটিতে তাৎক্ষণিকভাবে এমন অবিকল বিপরীতমুখী অবিরাম কারেন্ট আবিষ্ট হয় যা বহিঃস্থ পরিবর্তনকে এক চুলও রিংয়ের মধ্য দিয়ে ঢুকতে দেয় না। ফলে সুপারকন্ডাক্টিং রিংয়ে আবদ্ধ ফ্লাক্স অনন্তকাল ধরে সংরক্ষিত বা ট্র্যাপড থাকে।</t>
@@ -1319,11 +1309,6 @@
           <t>$N$ পাক ও $A$ ক্ষেত্রফলের একটি কুণ্ডলীকে $B$ সুষম চৌম্বক ক্ষেত্রে তার একটি ব্যাসের সাপেক্ষে $\omega$ সুষম কৌণিক দ্রুতিতে ঘোরানো হচ্ছে। কুণ্ডলীতে আবিষ্ট তাৎক্ষণিক তড়িচ্চালক বলের রাশিমালা প্রতিপাদন করো এবং কখন এই বল সর্বোচ্চ ও কখন শূন্য হয় তা ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>যেকোনো সময় $t$-তে কুণ্ডলীর তলের অভিলম্ব চৌম্বক ক্ষেত্রের সাথে $\theta = \omega t$ কোণ উৎপন্ন করে। কুণ্ডলীর সাথে জড়িত চৌম্বক ফ্লাক্স $\Phi_B = B A \cos(\omega t)$। সমস্ত $N$ টি পাকের মোট ফ্লাক্স लिंকেজ $\lambda = N B A \cos(\omega t)$। ফ্যারাডের আবেশ সূত্রানুযায়ী আবিষ্ট তড়িচ্চালক বল: $\mathcal{E} = -\frac{d\lambda}{dt} = -N B A \frac{d}{dt}[\cos(\omega t)] = N B A \omega \sin(\omega t)$। ১) যখন কুণ্ডলীর তল ক্ষেত্রের সমান্তরাল ($\omega t = 90^\circ$ বা $270^\circ$), তখন ফ্লাক্স শূন্য কিন্তু ফ্লাক্স পরিবর্তনের হার $\frac{d\Phi_B}{dt}$ সর্বোচ্চ, ফলে আবিষ্ট বল সর্বোচ্চ ($\mathcal{E}_0 = N B A \omega$)। ২) যখন তল ক্ষেত্রের লম্ব ($\omega t = 0^\circ$ বা $180^\circ$), তখন ফ্লাক্স সর্বোচ্চ কিন্তু তার পরিবর্তনের হার শূন্য, ফলে তড়িচ্চালক বল শূন্য হয়।</t>
@@ -1369,11 +1354,6 @@
           <t>একটি অনুভূমিক দণ্ড চুম্বকের উত্তর মেরুর ওপর থেকে একটি তামার রিংকে অভিকর্ষের অধীনে খাড়া নিচে পড়তে দেওয়া হলো। রিংটির নিম্নমুখী ত্বরণ $a$ অভিকর্ষজ ত্বরণ $g$-এর চেয়ে কম, সমান নাকি বেশি হবে? রিংটি চুম্বকটিকে অতিক্রম করে নিচে চলে যাওয়ার সময় ত্বরণ কেমন হবে?</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>রিংটি যখন চুম্বকের উত্তর মেরুর দিকে নেমে আসে, তখন রিংয়ের মধ্য দিয়ে নিচের দিকে চৌম্বক ফ্লাক্স বৃদ্ধি পায়। লেঞ্জের সূত্রানুযায়ী রিংটিতে এমন দিকে কারেন্ট আবিষ্ট হয় যাতে রিংয়ের নিচের পৃষ্ঠে একটি উত্তর মেরু সৃষ্টি হয়। এই উত্তর মেরু চুম্বকের উত্তর মেরুকে বিকর্ষণ করে একটি খাড়া ঊর্ধ্বমুখী মন্দনকারী চৌম্বক বল $F_B$ তৈরি করে। ফলে নিট ত্বরণ $a = g - \frac{F_B}{m} &lt; g$। আবার রিংটি চুম্বক অতিক্রম করে যখন নিচে পড়তে থাকে, তখন ফ্লাক্স হ্রাস পায়। লেঞ্জের সূত্রানুযায়ী রিংটিতে বিপরীতমুখী কারেন্ট চলে যাতে এর ওপরের পৃষ্ঠে দক্ষিণ মেরু তৈরি হয়। এই দক্ষিণ মেরু চুম্বকের উত্তর মেরুর দিকে আকৃষ্ট হয়ে পুনরায় একটি খাড়া ঊর্ধ্বমুখী টান বল তৈরি করে। ফলে তখনও নিম্নমুখী ত্বরণ $a &lt; g$ বজায় থাকে।</t>
@@ -1419,11 +1399,6 @@
           <t>একটি ধাতব রিং এবং একটি সমআকারের কাঁচের রিং উভয়ের মধ্য দিয়েই একই হারে চৌম্বক ফ্লাক্স পরিবর্তন করা হলো ($\frac{d\Phi_B}{dt}$ একই)। উভয় রিংয়ে আবিষ্ট তড়িৎক্ষেত্র, তড়িচ্চালক বল এবং প্রবাহিত কারেন্টের মানের তুলনা করো।</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>ম্যাক্সওয়েলের সাধারণীকৃত ফ্যারাডের সূত্রানুযায়ী $\oint \vec{E} \cdot d\vec{\ell} = -\frac{d\Phi_B}{dt}$। আবিষ্ট নন-ইলেক্ট্রোস্ট্যাটিক ঘূর্ণায়মান তড়িৎক্ষেত্র $\vec{E}$ এবং তড়িচ্চালক বল $\mathcal{E}$ সম্পূর্ণরূপে স্থানের স্থানিক চৌম্বক ফ্লাক্সের পরিবর্তনের হারের ওপর নির্ভরশীল, সেখানে কোনো মাধ্যম বা পরিবাহী উপাদান উপস্থিত আছে কি নেই তার ওপর নয়। ফলে শূন্যস্থান, কাঁচ বা তামা সর্বত্রই আবিষ্ট ভোল্টেজ বা বল হুবহু এক। কিন্তু ওহমের সূত্রানুযায়ী কারেন্ট $i = \frac{\mathcal{E}}{R}$। তামার রোধ অতি ক্ষুদ্র হওয়ায় শক্তিশালী কারেন্ট ও লেঞ্জের প্রতিক্রিয়াশীল বল তৈরি হয়, কিন্তু কাঁচের রোধ অত্যন্ত উচ্চ বা অসীম হওয়ায় কোনো কার্যকর কারেন্ট চলে না।</t>
@@ -1469,11 +1444,6 @@
           <t>$L$ দৈর্ঘ্য, $w$ প্রস্থ ও $R$ রোধের একটি আয়তাকার পরিবাহী কুণ্ডলীকে একটি সুষম লম্ব চৌম্বক ক্ষেত্র $B$ থেকে স্থির দ্রুতি $v$-তে সম্পূর্ণ বাইরে টেনে আনা হলো। বাহ্যিক বল দ্বারা কৃতকাজ $W_{\text{ext}}$ নির্ণয় করো এবং দেখাও যে এই কাজ কুণ্ডলীর রোধে উৎপন্ন মোট জুল তাপের সমান।</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I8" t="inlineStr">
         <is>
           <t>কুণ্ডলীটি বের করার সময় আবিষ্ট তড়িচ্চালক বল $\mathcal{E} = B L v$। বর্তনীতে কারেন্ট $I = \frac{\mathcal{E}}{R} = \frac{B L v}{R}$। কুণ্ডলীর সম্মুখ বাহুর ওপর চৌম্বক বাধা বল $F_B = I L B = \frac{B^2 L^2 v}{R}$। ধ্রুবক বেগে টানতে বাহ্যিক প্রযুক্ত বল $F_{\text{ext}} = F_B$ হতে হবে। $w$ দূরত্ব অতিক্রম করে কুণ্ডলীটি সম্পূর্ণ বের করতে বাহ্যিক বলের কাজ: $W_{\text{ext}} = F_{\text{ext}} \cdot w = \frac{B^2 L^2 v w}{R}$। অপরদিকে সময়কাল $t = \frac{w}{v}$। রোধে উৎপন্ন মোট জুল তাপ $H = I^2 R t = \left(\frac{B L v}{R}\right)^2 R \left(\frac{w}{v}\right) = \frac{B^2 L^2 v^2}{R} \frac{w}{v} = \frac{B^2 L^2 v w}{R}$। স্পষ্টতই $W_{\text{ext}} = H$, যা শক্তি সংরক্ষণশীলতার একটি নিখুঁত প্রমাণ।</t>
@@ -1519,11 +1489,6 @@
           <t>ক্ষেত্রফল ভেক্টর $\vec{A} = (2\hat{i} + 3\hat{j} - \hat{k})\text{ m}^2$ বিশিষ্ট একটি সমতল লুপ এমন একটি অঞ্চলে অবস্থিত যেখানে চৌম্বক ক্ষেত্র সময়ের সাথে পরিবর্তিত হয়: $\vec{B}(t) = (3 t^2 \hat{i} - 2 t \hat{j} + 4 \hat{k})\text{ T}$। $t = 2\text{ s}$ মুহূর্তে লুপটিতে আবিষ্ট তড়িচ্চালক বলের মান কত?</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>চৌম্বক ফ্লাক্সের ভেক্টর সমীকরণ $\Phi_B(t) = \vec{B}(t) \cdot \vec{A}$। ডট গুণন করে: $\Phi_B(t) = (3 t^2)(2) + (-2 t)(3) + (4)(-1) = 6 t^2 - 6 t - 4\text{ Wb}$। ফ্যারাডের সূত্রানুযায়ী আবিষ্ট তড়িচ্চালক বল: $\mathcal{E}(t) = -\frac{d\Phi_B}{dt} = -\frac{d}{dt}(6 t^2 - 6 t - 4) = -(12 t - 6) = 6 - 12 t$ ভোল্ট। $t = 2\text{ s}$ মুহূর্তে: $\mathcal{E}(2) = 6 - 12(2) = 6 - 24 = -18\text{ V}$। অতএব আবিষ্ট তড়িচ্চালক বলের মান $|\mathcal{E}| = 18\text{ V}$।</t>
@@ -1569,11 +1534,6 @@
           <t>একটি দীর্ঘ সরু সলিনয়েডের ভেতর সুষম পরিবর্তনশীল চৌম্বক ফ্লাক্স $\Phi_B(t)$ বিদ্যমান, কিন্তু সলিনয়েডের বাইরে ক্ষেত্র শূন্য। সলিনয়েডটিকে ঘিরে বাইরে স্থাপন করা একটি বৃহত্তর পরিবাহী লুপে তড়িচ্চালক বল আবিষ্ট হবে কি? লুপটির অবস্থানে স্থানীয় চৌম্বক ক্ষেত্র শূন্য হওয়া সত্ত্বেও কীভাবে আবেশ ঘটে?</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>ফ্যারাডের সমাকলন রূপ $\mathcal{E} = -\frac{d}{dt}\iint \vec{B} \cdot d\vec{A}$ স্পষ্ট নির্দেশ করে যে তারের নিজের অবস্থানে ক্ষেত্র শূন্য কি না তা বিবেচ্য নয়, বরং লুপটি দ্বারা বেষ্টিত সমগ্র এলাকার মোট চৌম্বক ফ্লাক্স পরিবর্তিত হচ্ছে কি না তা-ই মুখ্য। ম্যাক্সওয়েলের সূত্রে $\nabla \times \vec{E} = -\frac{\partial \vec{B}}{\partial t}$। সলিনয়েডের অভ্যন্তরে ফ্লাক্স পরিবর্তন চারপাশের বহিরাংশে বৃত্তাকার বলরেখা বিশিষ্ট একটি ঘূর্ণায়মান তড়িৎক্ষেত্র $\vec{E}$ আবিষ্ট করে। এই প্ররোচিত তড়িৎক্ষেত্রটি সলিনয়েডের বাইরে থাকা লুপের ইলেকট্রনগুলোর ওপর বল প্রয়োগ করে কারেন্ট প্রবাহিত করে।</t>
@@ -1619,11 +1579,6 @@
           <t>একটি শিথিল ও নমনীয় পরিবাহী তারের কুণ্ডলীকে একটি সুষম চৌম্বক ক্ষেত্রে রাখা হলো। কুণ্ডলীটির মধ্য দিয়ে কারেন্ট চালনা করলে এটি স্বতঃস্ফূর্তভাবে প্রসারিত হয়ে একটি নিখুঁত বৃত্তাকার রূপ নেয় কেন? ফ্লাক্স সর্বোচ্চকরণের দৃষ্টিকোণ থেকে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>দুটি দৃষ্টিকোণ থেকে এটি ব্যাখ্যা করা যায়: (১) বলের দৃষ্টিকোণ: কুণ্ডলীর মধ্য দিয়ে একই অভিমুখে কারেন্ট চললে তারের সংলগ্ন অংশগুলোতে সমান্তরাল কারেন্ট আকর্ষণ করে কিন্তু বিপরীতমুখী অংশগুলো বিকর্ষণ করে। তদুপরি বহিঃস্থ চৌম্বক ক্ষেত্রের সাথে মিথস্ক্রিয়ায় তারের প্রতিটি অংশের ওপর বহির্মুখী লম্ব লরেন্টজ বল ক্রিয়া করে যা তারটিকে বাইরের দিকে টানে। (২) শক্তির দৃষ্টিকোণ: একটি নির্দিষ্ট পরিসীমার মধ্যে বৃত্তই হলো সেই জ্যামিতিক চিত্র যার ক্ষেত্রফল সর্বোচ্চ। ফ্লাক্স সর্বোচ্চ হলে কুণ্ডলীর স্বকীয় আবেশ শক্তি $U = \frac{1}{2} L I^2$ সর্বোচ্চ হয়, যার জন্য ব্যবস্থাটি ন্যূনতম বাধায় স্থিতিশীল বৃত্তাকার রূপ লাভ করে।</t>
@@ -1669,11 +1624,6 @@
           <t>$L$ দৈর্ঘ্যের একটি ধাতব পরিবাহী দণ্ড একটি সুষম লম্ব চৌম্বক ক্ষেত্র $B$-তে ক্ষেত্রের লম্ব বরাবর $v$ বেগে গতিশীল। দণ্ডের ভেতরে মুক্ত ইলেকট্রনের ওপর ক্রিয়াশীল লরেন্টজ বলের ভিত্তিতে প্রমাণ করো যে দণ্ডটির দুই প্রান্তের মধ্যবর্তী গতিশীল তড়িচ্চালক বল $\mathcal{E} = B v L$।</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>দণ্ডটি $v$ বেগে চললে এর ভেতরের প্রতিটি মুক্ত ইলেকট্রনও $v$ বেগে গতিশীল হয়। ফলে প্রতিটি ইলেকট্রনের ওপর নিম্নমুখী চৌম্বক লরেন্টজ বল প্রযুক্ত হয়: $F_B = -e (\vec{v} \times \vec{B})$। এই বল ইলেকট্রনগুলোকে দণ্ডের এক প্রান্তে পুঞ্জীভূত করে, ফলে অপর প্রান্তে ধনাত্মক আধানের আধিক্য সৃষ্টি হয়। এই আধান পৃথকীকরণের কারণে দণ্ডের ভেতরে একটি স্থিরতড়িৎ ক্ষেত্র $\vec{E}$ আবিষ্ট হয় যা ইলেকট্রনের ওপর বিপরীতমুখী বল $F_E = e E$ প্রয়োগ করে। ভারসাম্যে: $e E = e v B \implies E = v B$। অতএব দুই প্রান্তের বিভব পার্থক্য বা তড়িচ্চালক বল $\mathcal{E} = \int_0^L E d\ell = E L = B v L$।</t>
@@ -1719,11 +1669,6 @@
           <t>$L$ দৈর্ঘ্যের একটি পরিবাহী দণ্ডের এক প্রান্তকে কেন্দ্র করে অপর প্রান্তটি একটি সুষম লম্ব চৌম্বক ক্ষেত্র $B$-তে ধ্রুবক কৌণিক দ্রুতি $\omega$-তে আবর্তিত হচ্ছে। দণ্ডটির কেন্দ্র ও প্রান্তের মধ্যবর্তী আবিষ্ট তড়িচ্চালক বল $\mathcal{E} = \frac{1}{2} B \omega L^2$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>ঘূর্ণন অক্ষ থেকে $r$ দূরত্বে অবস্থিত $dr$ দৈর্ঘ্যের একটি অতিক্ষুদ্র অংশ বিবেচনা করি। এই অংশের রৈখিক দ্রুতি $v(r) = \omega r$। ক্ষুদ্র অংশটিতে আবিষ্ট গতিশীল তড়িচ্চালক বল $d\mathcal{E} = B v(r) dr = B (\omega r) dr$। সমগ্র দণ্ডটির জন্য কেন্দ্র ($r=0$) থেকে প্রান্ত ($r=L$) পর্যন্ত সমাকলন করে: $\mathcal{E} = \int_0^L d\mathcal{E} = B \omega \int_0^L r dr = B \omega \left[\frac{r^2}{2}\right]_0^L = \frac{1}{2} B \omega L^2$। ফ্লাক্স কাটার দৃষ্টিকোণ থেকেও একই ফল পাওয়া যায়: এক পর্যায়কালে ($T = 2\pi/\omega$) দণ্ডটি একটি পূর্ণ বৃত্তাকার ক্ষেত্রফল $A = \pi L^2$ সুইপ করে। ফলে $\mathcal{E} = \frac{\Delta \Phi}{T} = \frac{B (\pi L^2)}{2\pi / \omega} = \frac{1}{2} B \omega L^2$।</t>
@@ -1769,11 +1714,6 @@
           <t>ফ্যারাডের ধাতব ডিস্ক জেনারেটরে $R$ ব্যাসার্ধের একটি তামার চাকতি অক্ষীয় সুষম চৌম্বক ক্ষেত্র $B$-তে $\omega$ কৌণিক বেগে ঘুরছে। চাকতির কেন্দ্র ও পরিধির মাঝে সংযুক্ত বহিস্থ রোধে উৎপন্ন তড়িচ্চালক বলের মান কত? ডিস্কটিতে কোনো ফ্লাক্স পরিবর্তন না হওয়া সত্ত্বেও কেন নিরবচ্ছিন্ন ডিসি বিদ্যুৎ উৎপন্ন হয়?</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>ফ্যারাডের সমমেরু জেনারেটর একটি অনন্য ঐতিহাসিক যন্ত্র। এখানে কোনো এসি রূপান্তর বা কম্যুটেটর ছাড়াই খাঁটি সমপ্রবাহ (DC) উৎপন্ন হয়। ডিস্কের ব্যাসার্ধ বরাবর প্রতিটি ইলেকট্রন চৌম্বক ক্ষেত্রের সাথে লম্বভাবে গতিশীল থাকায় কেন্দ্র থেকে পরিধির দিকে ব্যাসার্ধীয় লরেন্টজ বল লাভ করে। প্রতিটি ব্যাসার্ধীয় রেখায় আবিষ্ট তড়িচ্চালক বল $\mathcal{E} = \int_0^R B (\omega r) dr = \frac{1}{2} B \omega R^2$। ডিস্কটি সম্পূর্ণ প্রতিসম হওয়ায় কুণ্ডলীর ভেতর কোনো ফ্লাক্স পরিবর্তনের দৃশ্যমান হার নেই, তবুও লরেন্টজ বল অবিরাম সক্রিয় থাকে। এটি প্রমাণ করে যে ফ্যারাডের আবেশ মূলত দুটি স্বতন্ত্র ভৌতিক প্রক্রিয়ার সমষ্টি: পরিবর্তনশীল ক্ষেত্রের জন্য ম্যাক্সওয়েল ক্ষেত্র এবং গতিশীল পরিবাহীর জন্য লরেন্টজ বল।</t>
@@ -1819,11 +1759,6 @@
           <t>ব্যবধান $L$ এবং রোধ $R$ বিশিষ্ট দুটি সমান্তরাল অনুভূমিক মসৃণ পরিবাহী রেলের ওপর $m$ ভরের একটি দণ্ডকে প্রাথমিক বেগ $v_0$ দিয়ে একটি সুষম লম্ব চৌম্বক ক্ষেত্র $B$-তে ছেড়ে দেওয়া হলো। দণ্ডটির বেগ সময়ের সাথে কীভাবে হ্রাস পায় এবং থেমে যাওয়ার পূর্ব পর্যন্ত অতিক্রান্ত মোট দূরত্ব $x_{\max}$ কত?</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>যেকোনো বেগ $v$-তে আবিষ্ট তড়িচ্চালক বল $\mathcal{E} = B L v$ এবং কারেন্ট $I = \frac{B L v}{R}$। দণ্ডটির ওপর লেঞ্জের প্রতিক্রিয়াশীল চৌম্বক মন্দন বল $F = I L B = \frac{B^2 L^2 v}{R}$। গতির দ্বিতীয় সূত্রানুযায়ী: $m \frac{dv}{dt} = -\frac{B^2 L^2}{R} v \implies \frac{dv}{v} = -\left(\frac{B^2 L^2}{m R}\right) dt$। সমাকলন করে পাই: $v(t) = v_0 e^{-t/\tau}$, যেখানে বৈশিষ্ট্যমূলক ব্রেকিং সময় ধ্রুবক $\tau = \frac{m R}{B^2 L^2}$। অতিক্রান্ত দূরত্ব: $x_{\max} = \int_0^\infty v(t) dt = v_0 \int_0^\infty e^{-t/\tau} dt = v_0 \tau = \frac{m v_0 R}{B^2 L^2}$। কাজ-শক্তি উপপাদ্য অনুসারে দণ্ডের সম্পূর্ণ প্রাথমিক গতিশক্তি $\frac{1}{2}m v_0^2$ রোধে তাপে রূপান্তরিত হয়ে মিলিয়ে যায়।</t>
@@ -1869,11 +1804,6 @@
           <t>ব্যবধান $L$ বিশিষ্ট দুটি খাড়া উল্লম্ব পরিবাহী রেলের শীর্ষবিন্দুতে একটি রোধক $R$ যুক্ত। অনুভূমিক সুষম চৌম্বক ক্ষেত্র $B$-তে অভিকর্ষের অধীনে পতনশীল $m$ ভরের একটি পরিবাহী দণ্ড অর্জিত চূড়ান্ত প্রান্তীয় বেগ (terminal velocity, $v_t$)-এর রাশিমালা প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I16" t="inlineStr">
         <is>
           <t>পতনের সময় বেগ $v$ হলে আবিষ্ট গতিশীল তড়িচ্চালক বল $\mathcal{E} = B L v$ এবং রোধে কারেন্ট $I = \frac{B L v}{R}$। দণ্ডটির ওপর ঊর্ধ্বমুখী চৌম্বক ব্রেকিং বল $F_B = I L B = \frac{B^2 L^2 v}{R}$ এবং নিম্নমুখী অভিকর্ষীয় বল $W = m g$। দণ্ডটির ত্বরণ $a = g - \frac{B^2 L^2}{m R} v$। যখন বেগ বৃদ্ধি পেয়ে ঊর্ধ্বমুখী চৌম্বক বল ওজনের সমান হয়, তখন ত্বরণ শূন্য হয় এবং দণ্ডটি প্রান্তিক বেগে পৌঁছায়: $F_B = m g \implies \frac{B^2 L^2 v_t}{R} = m g \implies v_t = \frac{m g R}{B^2 L^2}$। এই অবস্থায় প্রতি সেকেন্ডে অভিকর্ষ দ্বারা সরবরাহকৃত ক্ষমতা ($m g v_t$) হুবহু রোধে জুল তাপ উৎপাদনের হারের ($I^2 R$) সমান হয়।</t>
@@ -1919,11 +1849,6 @@
           <t>তড়িচ্চুম্বকের দুটি মেরুমুখের মাঝে ঝুলন্ত একটি তামার নিরেট পাতকে দোলালে তা মুহূর্তে থেমে যায়, কিন্তু পাতটিতে চিরুনির মতো খাঁজ (slots) কাটলে তা বহুক্ষণ ধরে দুলতে থাকে কেন? ইলেক্ট্রোম্যাগনেটিক ড্যাম্পিংয়ের মূলনীতি ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>যখন নিরেট তামার পাতটি চৌম্বক ক্ষেত্রের মধ্যে প্রবেশ করে বা বের হয়, তখন পাতের ধাতব তলের ভেতর ফ্লাক্সের পরিবর্তনের কারণে বিশাল বৃত্তাকার ঘূর্ণি প্রবাহ (এডি কারেন্ট) আবিষ্ট হয়। লেঞ্জের সূত্রানুযায়ী এই কারেন্টগুলোর ওপর ক্রিয়াশীল চৌম্বক বল সর্বদা পাতের গতির বিপরীত অভিমুখে একটি শক্তিশালী ব্রেকিং বল সৃষ্টি করে। ফলে পাতের সমস্ত যান্ত্রিক গতিশক্তি কয়েক সেকেন্ডের মধ্যে রোধীয় জুল তাপে অপচয় হয়ে পাতটি অবিলম্বে নিশ্চল হয়ে যায় (ইলেক্ট্রোম্যাগনেটিক ব্রেকিং)। পাতটিতে খাঁজ কাটলে ঘূর্ণি প্রবাহের মুক্ত বৃত্তাকার পথগুলো ভেঙে ক্ষুদ্র ক্ষুদ্র খণ্ডে বিভক্ত হয় এবং পথের কার্যকর বৈদ্যুতিক রোধ বহুগুণ বৃদ্ধি পায়। ফলে এডি কারেন্টের মান অত্যন্ত সংকুচিত হয় এবং বিরোধী বল নগণ্য হওয়ায় পাতটি বাধাহীনভাবে বহুক্ষণ দুলতে পারে।</t>
@@ -1969,11 +1894,6 @@
           <t>$L = 30\text{ m}$ ডানার বিস্তার (wingspan) বিশিষ্ট একটি উড়োজাহাজ অনুভূমিকভাবে $v = 900\text{ km/h}$ বেগে উত্তর দিকে উড়ে যাচ্ছে। ঐ স্থানে ভূ-চৌম্বক ক্ষেত্রের উল্লম্ব উপাংশ $B_V = 4 \times 10^{-5}\text{ T}$ হলে বিমানের দুই ডানার প্রান্তের মধ্যে আবিষ্ট তড়িচ্চালক বল কত? এই বিভব দিয়ে কি বিমানের ভেতরের বাতি জ্বালানো সম্ভব?</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>বিমানের বেগ $v = 900 \times \frac{5}{18} = 250\text{ m/s}$। ডানাটি অনুভূমিক হওয়ায় এটি কেবল ভূ-চৌম্বক ক্ষেত্রের উল্লম্ব উপাংশকে ছেদ করে। আবিষ্ট গতিশীল তড়িচ্চালক বল $\mathcal{E} = B_V L v = (4 \times 10^{-5}\text{ T})(30\text{ m})(250\text{ m/s}) = 0.3\text{ V}$। ডান হাতের নিয়মে ইলেকট্রনগুলো ডান ডানার দিকে ধাবিত হয়, ফলে বাম ডানা ধনাত্মক বিভবে থাকে। তবে এই ভোল্টেজ দিয়ে বিমানের ভেতরে বাতি জ্বালানো অসম্ভব। কারণ একটি বাতি যুক্ত করে বর্তনী সম্পূর্ণ করতে হলে সংযোগকারী তারকেও বিমানের সাথে একই গতিতে চলতে হবে। ফলে সংযোগ তারেও হুবহু সমমানের তড়িচ্চালক বল ($0.3\text{ V}$) একই অভিমুখে আবিষ্ট হবে, যার ফলে সম্পূর্ণ বদ্ধ লুপে কির্শফের ভোল্টেজ নিয়মে নিট কারেন্ট হুবহু শূন্য হবে।</t>
@@ -2019,11 +1939,6 @@
           <t>একটি পাতলা তামার চাকতি তার অক্ষের সাপেক্ষে ঘুরছে এবং এর একটি প্রান্তের ক্ষুদ্র অংশে একটি লম্ব সুষম চৌম্বক ক্ষেত্র $B$ প্রয়োগ করা হলো। চাকতিটির ওপর একটি বিপরীতমুখী ঘূর্ণন প্রতিরোধী টর্ক ক্রিয়া করে কেন? বৈদ্যুতিক অ্যানালগ ওয়াট-আওয়ার মিটারে এই নীতির প্রয়োগ ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>চাকতির যে অংশটি চৌম্বক ক্ষেত্রে প্রবেশ করে এবং বের হয়, সেখানে গতিশীল তড়িচ্চালক বলের কারণে স্থানীয় বদ্ধ এডি কারেন্ট লুপ তৈরি হয়। চৌম্বক ক্ষেত্রের সাথে এই এডি কারেন্টের মিথস্ক্রিয়ায় একটি বিপরীতমুখী চৌম্বক বল $F \propto B^2 \omega$ উৎপন্ন হয়, যা ঘূর্ণন অক্ষের সাপেক্ষে একটি লরেন্টজ ব্রেকিং টর্ক $\tau_{\text{brake}} = -k B^2 \omega$ সৃষ্টি করে। অ্যানালগ বিদ্যুৎ মিটারে সরবরাহকৃত বৈদ্যুতিক শক্তি ঘোরানো টর্ক ($\tau_{\text{drive}} \propto P$) সৃষ্টি করে। স্থায়ী চুম্বকের তৈরি ব্রেকিং টর্ক এর সমানুপাতিক ভারসাম্যে পৌঁছে: $k B^2 \omega = \tau_{\text{drive}} \propto P \implies \omega \propto P$। ফলে চাকতির ঘূর্ণন বেগ সরাসরি ব্যবহৃত বৈদ্যুতিক ক্ষমতার সমানুপাতিক হয় এবং ঘূর্ণন সংখ্যা মেপে কিলোওয়াট-ঘণ্টা (kWh) ইউনিট রেকর্ড করা যায়।</t>
@@ -2120,11 +2035,6 @@
           <t>একটি নমনীয় বৃত্তাকার পরিবাহী তারকে অনুভূমিকভাবে একটি শক্তিশালী উল্লম্ব অপসারী চৌম্বক ক্ষেত্রে নিক্ষেপ করা হলে এর আকার প্রসারিত নাকি সংকুচিত হবে? লেঞ্জের সূত্রের সাহায্যে ব্যাখ্যা করো।</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>লেঞ্জের সাধারণীকৃত নীতি অনুসারে, ব্যবস্থাটি কেবল তড়িৎ প্রবাহের মাধ্যমেই ফ্লাক্স পরিবর্তনের বিরোধিতা করে না, বরং যান্ত্রিক আকার পরিবর্তনের সুযোগ থাকলে নিজের ক্ষেত্রফলকেও পরিবর্তন করে। যখন রিংটি বর্ধনশীল চৌম্বক ক্ষেত্রে প্রবেশ করে, তখন ফ্লাক্স $\Phi = B A$ বৃদ্ধি পায়। ফ্লাক্স বৃদ্ধি কমাতে রিংয়ে এমন কারেন্ট আবিষ্ট হয় যার ব্যাসার্ধীয় লরেন্টজ বল কেন্দ্রমুখী হয় এবং রিংটিকে সংকুচিত করে ক্ষেত্রফল $A$ কমিয়ে দেয়। বিপরীতে দুর্বল ক্ষেত্রের দিকে ছিটকে যাওয়ার সময় ফ্লাক্স ধরে রাখতে ব্যাসার্ধীয় বল বহির্মুখী হয় এবং রিংটিকে প্রসারিত করে।</t>
@@ -2170,11 +2080,6 @@
           <t>ম্যাক্সওয়েলের তৃতীয় সমীকরণ $\nabla \times \vec{E} = -\frac{\partial \vec{B}}{\partial t}$ থেকে প্রমাণ করো যে পরিবর্তনশীল চৌম্বক ক্ষেত্র দ্বারা আবিষ্ট তড়িৎক্ষেত্র একটি অসংরক্ষণশীল (non-conservative) ক্ষেত্র। স্থিরতড়িৎ ক্ষেত্রের সাথে এর মূল পার্থক্য কী?</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>স্থিরতড়িৎ ক্ষেত্রে স্থির আধানের কারণে $\nabla \times \vec{E} = 0$, ফলে যেকোনো বদ্ধ লুপে কৃতকাজ শূন্য ($\oint \vec{E} \cdot d\vec{\ell} = 0$) এবং একটি সুনির্দিষ্ট বিভব $V$ সংজ্ঞায়িত করা যায়। কিন্তু সময়-পরিবর্তনশীল চৌম্বক ক্ষেত্র স্থানে যে তড়িৎক্ষেত্র $\vec{E}_{\text{ind}}$ সৃষ্টি করে তার কার্ল অশূন্য: $\nabla \times \vec{E}_{\text{ind}} = -\frac{\partial \vec{B}}{\partial t}$। স্টোকসের উপপাদ্য প্রয়োগ করলে পাই: $\oint \vec{E}_{\text{ind}} \cdot d\vec{\ell} = -\iint \frac{\partial \vec{B}}{\partial t} \cdot d\vec{A} = -\frac{d\Phi_B}{dt} \neq 0$। অর্থাৎ একটি বদ্ধ লুপ বরাবর আধানকে একবার ঘুরিয়ে আনলে নিট কাজ সম্পন্ন হয়। এই বলরেখাগুলো চৌম্বক বলরেখার ন্যায় নিখুঁত বদ্ধ লুপ তৈরি করে, কোনো বিন্দু আধান থেকে শুরু বা শেষ হয় না। ফলে এই ক্ষেত্রে কোনো একক-মানবিশিষ্ট স্কেলার বিভব $V$ থাকা অসম্ভব।</t>
@@ -2220,11 +2125,6 @@
           <t>$R$ ব্যাসার্ধের একটি দীর্ঘ চোঙাকার অঞ্চলে সুষম চৌম্বক ক্ষেত্র বিদ্যমান যা সময়ের সাথে সুষম হারে বৃদ্ধি পাচ্ছে ($\frac{dB}{dt} = \alpha$)। অক্ষ থেকে $r$ দূরত্বে প্ররোচিত তড়িৎক্ষেত্র $E(r)$-এর মান (ক) $r \le R$ এবং (খ) $r \ge R$ অঞ্চলের জন্য নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>ক) চোঙের অভ্যন্তরে ($r \le R$) অক্ষকে কেন্দ্র করে $r$ ব্যাসার্ধের একটি বৃত্তাকার লুপ বিবেচনা করি। প্রতিসাম্যের কারণে তড়িৎক্ষেত্রের দিক স্পর্শকীয় এবং মান ধ্রুবক। সমাকলন রূপ: $\oint \vec{E} \cdot d\vec{\ell} = E (2\pi r) = \left|\frac{d\Phi_B}{dt}\right| = \frac{d}{dt}(B \pi r^2) = \pi r^2 \frac{dB}{dt}$। অতএব $E (2\pi r) = \pi r^2 \alpha \implies E(r) = \frac{r}{2}\alpha$। খ) চোঙের বাইরে ($r \ge R$) লুপের ভেতর মোট আবদ্ধ ফ্লাক্স ধ্রুবক এলাকার জন্য প্রযোজ্য: $\Phi_B = B (\pi R^2)$। অতএব $E (2\pi r) = \pi R^2 \frac{dB}{dt} = \pi R^2 \alpha \implies E(r) = \frac{R^2}{2r}\alpha$। লক্ষণীয় যে বাইরে চৌম্বক ক্ষেত্র শূন্য হলেও সেখানে প্ররোচিত তড়িৎক্ষেত্র বিদ্যমান এবং তা দূরত্বের ব্যস্তানুপাতে হ্রাস পায়।</t>
@@ -2270,11 +2170,6 @@
           <t>ওয়াল্টার লুইনের বিখ্যাত ভোল্টমিটার প্যারাডক্স ব্যাখ্যা করো: পরিবর্তনশীল চৌম্বক ফ্লাক্স বেষ্টনকারী একটি বৃত্তাকার পরিবাহী লুপে দুটি ভিন্ন রোধ $R_1$ ও $R_2$ শ্রেণীতে যুক্ত। একই দুটি বিন্দু $A$ ও $B$-এর মাঝে দুটি অভিন্ন ভোল্টমিটার দুই পাশ থেকে যুক্ত করলে তারা দুটি সম্পূর্ণ ভিন্ন মান প্রদর্শন করে কেন?</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>লুপটিতে মোট আবিষ্ট তড়িচ্চালক বল $\mathcal{E}$ হলে কারেন্ট $i = \frac{\mathcal{E}}{R_1 + R_2}$। একটি ভোল্টমিটার $V_1$ বাম পাশ থেকে এবং অপর ভোল্টমিটার $V_2$ ডান পাশ থেকে বিন্দু $A$ ও $B$-তে যুক্ত করা হলো। $V_1$ এবং রোধ $R_1$ মিলে গঠিত লুপে কোনো চৌম্বক ফ্লাক্স আবদ্ধ নেই, ফলে KVL অনুযায়ী $V_1 + i R_1 = 0 \implies V_1 = -i R_1$। কিন্তু $V_2$ এবং রোধ $R_2$ মিলে গঠিত লুপেও কোনো ফ্লাক্স নেই, ফলে $V_2 - i R_2 = 0 \implies V_2 = i R_2$। যদি $R_1 = 100\ \Omega$ এবং $R_2 = 900\ \Omega$ হয়, তবে একই দুটি বিন্দুর মাঝে একটি ভোল্টমিটার পাঠ দেবে $-0.1\text{ V}$ এবং অন্যটি পাঠ দেবে $+0.9\text{ V}$! এটি কোনো যন্ত্রের ত্রুটি নয়, বরং অসংরক্ষণশীল ক্ষেত্রে ভোল্টমিটারের তারের অবস্থানই পরিমাপ্য ফ্লাক্সকে নির্ধারণ করে।</t>
@@ -2320,11 +2215,6 @@
           <t>ইলেকট্রন ত্বরক যন্ত্র বেটাট্রনে (Betatron) পরিবর্তনশীল চৌম্বক ক্ষেত্র যুগপৎভাবে দুটি কাজ করে: কণার কক্ষপথের ব্যাসার্ধ $R$ স্থির রাখে এবং কণাকে ত্বরান্বিত করে। প্রমাণ করো যে স্থির ব্যাসার্ধের কক্ষপথ বজায় রাখার জন্য প্রয়োজনীয় বেটাট্রন শর্ত হলো কক্ষপথের অভ্যন্তরে গড় চৌম্বক ক্ষেত্র কক্ষপথের অবস্থানের স্থানীয় ক্ষেত্রের ঠিক দ্বিগুণ হতে হয় ($\langle B \rangle = 2 B_R$)।</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>কক্ষপথের পরিধি বরাবর প্ররোচিত তড়িৎক্ষেত্র: $E (2\pi R) = \frac{d\Phi_B}{dt} \implies E = \frac{1}{2\pi R}\frac{d\Phi_B}{dt}$। নিউটনের দ্বিতীয় সূত্রানুযায়ী ভরবেগ বৃদ্ধির হার: $\frac{dp}{dt} = e E = \frac{e}{2\pi R}\frac{d\Phi_B}{dt}$। সময় সাপেক্ষে সমাকলন করলে ভরবেগ: $p = \frac{e}{2\pi R}\Delta \Phi_B$। আবার $R$ ব্যাসার্ধের বৃত্তাকার কক্ষপথে ঘূর্ণনের জন্য লরেন্টজ বলের কেন্দ্রমুখী সমীকরণ: $p = e R B_R$। সমীকরণ দুটি তুলনা করলে পাই: $e R B_R = \frac{e}{2\pi R}\Delta \Phi_B \implies \Delta \Phi_B = 2\pi R^2 B_R$। কিন্তু গড় ক্ষেত্রের সংজ্ঞামতে $\Phi_B = \langle B \rangle (\pi R^2)$। অতএব $\langle B \rangle (\pi R^2) = 2\pi R^2 B_R \implies \langle B \rangle = 2 B_R$। এই শর্ত পূরণের জন্য বেটাট্রনের মেরুমুখগুলোকে এমনভাবে তৈরি করা হয় যাতে কেন্দ্রে ক্ষেত্র তীব্র হয় এবং প্রান্তে কম হয়।</t>
@@ -2370,11 +2260,6 @@
           <t>একটি সুষম পরিবর্তনশীল চৌম্বক ক্ষেত্রে স্থাপিত একটি সুষম বৃত্তাকার পরিবাহী তারের কুণ্ডলীতে কোনো বিন্দুতেই স্থিরতড়িৎ আধান পুঞ্জীভূত হয় না ($\sigma = 0$), কিন্তু কুণ্ডলীটির কোনো অংশ কেটে একটি রোধক যুক্ত করলে তারের পৃষ্ঠে আধানের স্তূপ সৃষ্টি হয় কেন?</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>সুষম বৃত্তাকার রিংয়ে প্রতিসাম্যের কারণে প্রতিটি স্থানে প্ররোচিত নন-কনজারভেটিভ ক্ষেত্র $E_{\text{ind}}$ এবং কারেন্ট ঘনত্ব $J = \sigma_c E_{\text{ind}}$ হুবহু সামঞ্জস্যপূর্ণ। ফলে কোনো আধান পুঞ্জীভবনের প্রয়োজন হয় না। কিন্তু যখন রিংটির এক অংশে একটি কেন্দ্রীভূত রোধক $R$ বসানো হয়, তখন রোধকের ভেতরে বিপুল কারেন্ট চালাতে একটি তীব্র তড়িৎক্ষেত্র প্রয়োজন কিন্তু নন-কনজারভেটিভ ক্ষেত্র সর্বত্র সুষম। এই অসামঞ্জস্য দূর করতে বর্তনীর বিভিন্ন বাঁকে ও রোধকের দুই প্রান্তে স্বয়ংক্রিয়ভাবে স্থিরতড়িৎ পৃষ্ঠ আধান জমা হয়। এই পৃষ্ঠ আধানগুলো একটি স্থিরতড়িৎ ক্ষেত্র $\vec{E}_{\text{es}}$ সৃষ্টি করে, যা রোধকের ভেতরে প্ররোচিত ক্ষেত্রের সাথে যোগ হয়ে প্রয়োজনীয় উচ্চ বিভব ড্রপ ঘটায় এবং অবশিষ্ট তারে ক্ষেত্রকে কমিয়ে দেয়।</t>
@@ -2420,11 +2305,6 @@
           <t>একটি পরিবর্তনশীল চৌম্বক ক্ষেত্রে স্থাপিত একটি বৃত্তাকার তারের রিংয়ে একটি ক্ষুদ্র ফাঁক (ছোট ফাঁকা অংশ) কেটে দেওয়া হলো। এই ফাঁকের দুই প্রান্তে উন্মুক্ত বিভব পার্থক্য কত হবে এবং তারের ধাতব অংশের ভেতরে নিট তড়িৎক্ষেত্র কত হবে?</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>রিংটিতে একটি ফাঁক থাকলে কোনো স্থায়ী কারেন্ট প্রবাহিত হতে পারে না ($I=0$)। ওহমের সূত্রানুযায়ী পরিবাহীর উপাদানের ভেতরে কারেন্ট শূন্য হলে নিট তড়িৎক্ষেত্র অবশ্যই শূন্য হতে হবে: $\vec{E}_{\text{net}} = 0$। প্ররোচিত নন-কনজারভেটিভ ক্ষেত্র $\vec{E}_{\text{ind}}$ তারের মুক্ত ইলেকট্রনগুলোকে ফাঁকের এক প্রান্তের দিকে ঠেলে দেয়, ফলে ফাঁকের দুই প্রান্তে সমান ও বিপরীত স্থিরতড়িৎ আধান জমা হয়। এই আধানগুলো ধাতুর অভ্যন্তরে একটি বিপরীতমুখী স্থিরতড়িৎ ক্ষেত্র $\vec{E}_{\text{es}}$ সৃষ্টি করে যা প্ররোচিত ক্ষেত্রকে হুবহু বাতিল করে দেয়: $\vec{E}_{\text{es}} = -\vec{E}_{\text{ind}}$। তবে ফাঁকা স্থানে এই স্থিরতড়িৎ ক্ষেত্রটি সক্রিয় থাকে। ফাঁকা স্থানের দুই প্রান্তে রেখা সমাকলন করলে সম্পূর্ণ তড়িচ্চালক বলের সমান বিভব পার্থক্য পাওয়া যায়: $V = \int_{\text{gap}} \vec{E}_{\text{es}} \cdot d\vec{\ell} = \mathcal{E} = -\frac{d\Phi_B}{dt}$।</t>
@@ -2470,11 +2350,6 @@
           <t>দুটি সমান ব্যাসার্ধের বৃত্তাকার লুপ একটি অপরটির ওপর রেখে একটি '৮' (৪-এর ন্যায় চিত্র বা figure-eight) আকারে বিপরীত মুখে পেঁচিয়ে একটি একক বদ্ধ বর্তনী তৈরি করা হলো। লুপ দুটির ভেতর দিয়ে সমান হারে পরিবর্তনশীল চৌম্বক ক্ষেত্র চালনা করলে বর্তনীতে মোট আবিষ্ট তড়িচ্চালক বল কত হবে?</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>ফিগার-এইট (Figure-8) লুপে তারটি এক লুপে ঘড়ির কাঁটার দিকে ঘুরলে অন্য লুপে ঘড়ির কাঁটার বিপরীত দিকে ঘোরে। ফলে দুটি লুপের ক্ষেত্রফল ভেক্টরের দিক পরস্পর ১৮০ ডিগ্রি বিপরীতমুখী হয়। প্রথম লুপের ফ্লাক্স $\Phi_1 = B A$ হলে দ্বিতীয় লুপের ফ্লাক্স $\Phi_2 = -B A$। সম্পূর্ণ বর্তনীর মোট ফ্লাক্স लिंকেজ $\Phi_{\text{net}} = \Phi_1 + \Phi_2 = B A - B A = 0$। যেহেতু মোট ফ্লাক্স শূন্য এবং সময়ের সাথে এর কোনো পরিবর্তন নেই, তাই ফ্যারাডের সূত্রানুযায়ী মোট আবিষ্ট তড়িচ্চালক বল $\mathcal{E}_{\text{net}} = -\frac{d\Phi_{\text{net}}}{dt} = 0$। কোনো নিট কারেন্ট প্রবাহিত হবে না।</t>
@@ -2520,11 +2395,6 @@
           <t>একটি পরিবর্তনশীল চৌম্বক ক্ষেত্রে শূন্য বেগ থেকে যাত্রা শুরু করা একটি মুক্ত আধান $+q$ বৃত্তাকার পথে ঘুরতে ঘুরতে গতিশক্তি অর্জন করে। চৌম্বক বল কোনো কাজ না করা সত্ত্বেও আধানটির গতিশক্তি বৃদ্ধির কারণ কী?</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>আমরা জানি যে খাঁটি চৌম্বক ক্ষেত্র $\vec{B}$ সর্বদা কণার বেগের সাথে লম্ব হওয়ায় কোনো কাজ করতে পারে না ($W_B = 0$)। কিন্তু সময়-পরিবর্তনশীল চৌম্বক ক্ষেত্র স্থানে একটি প্ররোচিত তড়িৎক্ষেত্র $\vec{E}_{\text{ind}}$ সৃষ্টি করে ($\nabla \times \vec{E} = -\frac{\partial \vec{B}}{\partial t}$)। এই তড়িৎক্ষেত্রটি কণার গতির স্পর্শক বরাবর বল প্রয়োগ করে: $\vec{F}_E = q \vec{E}_{\text{ind}}$। এই বলটি কণার সরণের সমান্তরাল হওয়ায় ধনাত্মক কাজ সম্পাদন করে: $W = \int q \vec{E}_{\text{ind}} \cdot d\vec{r} &gt; 0$। কাজ-শক্তি উপপাদ্য অনুসারে এই বাহ্যিক তড়িৎ বলের কাজই কণার গতিশক্তি ক্রমাগত বৃদ্ধি করে।</t>
@@ -2570,11 +2440,6 @@
           <t>বাহুর দৈর্ঘ্য $a$ বিশিষ্ট একটি বর্গাকার পরিবাহী লুপ একটি সুষম পরিবর্তনশীল চৌম্বক ক্ষেত্র $\frac{dB}{dt} = \alpha$-এর মধ্যে অবস্থিত। লুপটির প্রতিটি বাহুর রোধ $r$ হলে যেকোনো একটি বাহুর দুই প্রান্তের মধ্যবর্তী কার্যকর বিভব পার্থক্য কত?</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>বর্গাকার লুপের ক্ষেত্রফল $A = a^2$। মোট আবিষ্ট তড়িচ্চালক বল $\mathcal{E} = \frac{d\Phi_B}{dt} = a^2 \alpha$। চারটি বাহুর মোট রোধ $4r$ হওয়ায় বর্তনীতে প্রতিসম প্রবাহ $i = \frac{\mathcal{E}}{4r} = \frac{a^2 \alpha}{4r}$। যেকোনো একটি বাহুর জন্য প্রতিসাম্যের কারণে আবিষ্ট তড়িচ্চালক বলের চতুর্থাংশ বরাদ্দ থাকে: $\mathcal{E}_1 = \frac{\mathcal{E}}{4} = i r$। এই বাহুর দুই প্রান্তের বিভব পার্থক্য মাপলে ওহমীয় বিভব পতন এবং অভ্যন্তরীণ আবিষ্ট তড়িচ্চালক বল পরস্পরকে হুবহু নিষ্ক্রিয় করে দেয়: $V = \mathcal{E}_1 - i r = i r - i r = 0$। ফলে লুপের প্রতিটি শীর্ষবিন্দুর বিভব সমান থাকে এবং কোনো দুটি কোণার মাঝে বিভব পার্থক্য শূন্য হয়।</t>
@@ -2620,11 +2485,6 @@
           <t>আধুনিক ইন্ডাকশন কুকারে (Induction Cooker) রান্নার পাত্রের তলা প্রচণ্ড উত্তপ্ত হলেও কুকারের কাঁচের সিরামিক শীর্ষতল গরম হয় না কেন? রান্নার পাত্র তৈরিতে অ্যালুমিনিয়ামের চেয়ে ফেরোম্যাগনেটিক স্টিল বা ঢালাই লোহা কেন অনেক বেশি কার্যকর?</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I31" t="inlineStr">
         <is>
           <t>ইন্ডাকশন কুকারের কাঁচের প্লেটের নিচে তামার কুণ্ডলীতে ২০ থেকে ৪০ কিলোহার্জ কম্পাঙ্কের পরিবর্তী বিদ্যুৎ প্রবাহিত করা হয়। কাঁচ একটি চমৎকার অন্তরক হওয়ায় এতে কোনো এডি কারেন্ট উৎপন্ন হয় না, ফলে এটি সরাসরি গরম হয় না। যখন ওপরে ফেরোচৌম্বক পাত্র রাখা হয়, তখন পরিবর্তনশীল চৌম্বক ফ্লাক্স পাত্রের ধাতব তলায় শক্তিশালী এডি কারেন্ট এবং একই সাথে হিস্টেরেসিস লস ঘটায়। উচ্চ কম্পাঙ্কের কারণে স্কিন ইফেক্টের দরুন কারেন্ট কেবল পাত্রের নিচের অতি পাতলা স্তরে (প্রায় ০.১ মিমি) সীমাবদ্ধ থাকে, ফলে কার্যকর রোধ অনেক বৃদ্ধি পায় এবং $I^2 R$ জুল তাপে পাত্রটি দ্রুত উত্তপ্ত হয়। অ্যালুমিনিয়াম বা তামার রোধাঙ্ক অতি কম এবং প্রবেশ্যতা কম ($\mu_r \approx 1$) হওয়ায় তাদের স্কিন ডেপথ বেশি এবং কার্যকর রোধ নগণ্য, ফলে তারা পর্যাপ্ত তাপ উৎপন্ন করতে পারে না।</t>
@@ -2670,11 +2530,6 @@
           <t>স্বকীয় আবেশ গুণাঙ্ক (Self-inductance, $L$)-এর সংজ্ঞা দাও এবং হেনরি ($H$) এককের সংজ্ঞা লেখো। দৈর্ঘ্য $\ell$, প্রস্থচ্ছেদ ক্ষেত্রফল $A$ এবং মোট পাকসংখ্যা $N$ বিশিষ্ট একটি দীর্ঘ বায়বীয় সলিনয়েডের স্বকীয় আবেশ গুণাঙ্কের রাশিমালা $L = \mu_0 \frac{N^2 A}{\ell} = \mu_0 n^2 A \ell$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>কোনো কুণ্ডলীতে $I$ প্রবাহ চললে তার নিজের মধ্য দিয়ে অতিক্রান্ত ফ্লাক্স लिंকেজ $N \Phi_B$ প্রবাহের সমানুপাতিক: $N \Phi_B = L I \implies L = \frac{N \Phi_B}{I}$। ফ্যারাডের সূত্রে ব্যাক-ইএমএফ $\mathcal{E} = -L \frac{dI}{dt}$। যদি $\frac{dI}{dt} = 1\text{ A/s}$ এবং $\mathcal{E} = 1\text{ V}$ হয়, তবে $L = 1\text{ H}$। সলিনয়েডের ভেতরে চৌম্বক ক্ষেত্র $B = \mu_0 n I = \mu_0 \frac{N}{\ell} I$। একটি পাকের ফ্লাক্স $\Phi_B = B A = \frac{\mu_0 N I A}{\ell}$। সমস্ত $N$ টি পাকের মোট ফ্লাক্স लिंকেজ $N \Phi_B = \frac{\mu_0 N^2 A}{\ell} I$। সংজ্ঞার সাথে তুলনা করলে পাই: $L = \frac{\mu_0 N^2 A}{\ell} = \mu_0 n^2 A \ell$ (যেখানে $n = N/\ell$ হলো প্রতি একক দৈর্ঘ্যের পাকসংখ্যা)।</t>
@@ -2720,11 +2575,6 @@
           <t>পারস্পরিক আবেশ গুণাঙ্ক (Mutual Inductance, $M$)-এর সংজ্ঞা দাও। নিউম্যানের পারস্পরিক উপপাদ্য (Reciprocity Theorem) অনুসারে প্রমাণ করো যে দুটি কুণ্ডলীর আকার যাই হোক না কেন, প্রথম কুণ্ডলীর সাপেক্ষে দ্বিতীয়টির পারস্পরিক আবেশ এবং দ্বিতীয়টির সাপেক্ষে প্রথমটির পারস্পরিক আবেশ হুবহু সমান হয় ($M_{12} = M_{21} = M$)।</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>প্রথম কুণ্ডলীর কারেন্ট $I_1$-এর কারণে দ্বিতীয় কুণ্ডলীর মোট ফ্লাক্স लिंকেজ $N_2 \Phi_{21} = M_{21} I_1$। নিউম্যানের সূত্রানুযায়ী ভেক্টর বিভব প্রয়োগ করে দ্বিতীয় কুণ্ডলীর ফ্লাক্স সমাকলন করলে পাওয়া যায়: $M_{21} = \frac{\mu_0}{4\pi} \oint_{C_1} \oint_{C_2} \frac{d\vec{\ell}_1 \cdot d\vec{\ell}_2}{r_{12}}$। এই ডাবল লাইন ইন্টিগ্রালে কুণ্ডলী ১ এবং কুণ্ডলী ২-এর সূচক পরস্পর অদলবদল করলেও ডট গুণন $d\vec{\ell}_1 \cdot d\vec{\ell}_2$ এবং দূরত্ব $r_{12}$ অপরিবর্তিত থাকে। ফলে সমাকলনের মান হুবহু এক থাকে: $M_{12} = M_{21} = M$। এটি প্রমাণ করে যে একটি বৃহৎ কুণ্ডলীর মাঝে ক্ষুদ্র কুণ্ডলী রাখলে উভয়ের পারস্পরিক আবেশ সমান হয়।</t>
@@ -2770,11 +2620,6 @@
           <t>একই দৈর্ঘ্যের ($\ell$) দুটি সমাক্ষীয় দীর্ঘ সলিনয়েডের অভ্যন্তরীণ সলিনয়েডের ব্যাসার্ধ $r_1$ ও মোট পাকসংখ্যা $N_1$ এবং বহিঃস্থ সলিনয়েডের ব্যাসার্ধ $r_2$ ($r_2 &gt; r_1$) ও মোট পাকসংখ্যা $N_2$। সলিনয়েডদ্বয়ের পারস্পরিক আবেশ গুণাঙ্ক $M$-এর সমীকরণ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>হিসাবের সুবিধার্থে বহিঃস্থ সলিনয়েডে (২) কারেন্ট $I_2$ প্রবাহিত করি। এর অভ্যন্তরে চৌম্বক ক্ষেত্র সুষম: $B_2 = \mu_0 \frac{N_2}{\ell} I_2$। এই ক্ষেত্রটি অভ্যন্তরীণ সলিনয়েডের (১) প্রতিটি পাকের মধ্য দিয়ে অতিক্রম করে যার কার্যকর প্রস্থচ্ছেদ ক্ষেত্রফল $A_1 = \pi r_1^2$। প্রথম সলিনয়েডের একটি পাকের ফ্লাক্স $\Phi_1 = B_2 A_1 = \mu_0 \frac{N_2}{\ell} I_2 (\pi r_1^2)$। প্রথম সলিনয়েডের সমস্ত $N_1$ টি পাকের মোট ফ্লাক্স लिंকেজ: $\lambda_1 = N_1 \Phi_1 = \frac{\mu_0 N_1 N_2 \pi r_1^2}{\ell} I_2$। পারস্পরিক আবেশের সংজ্ঞামতে $\lambda_1 = M I_2$। অতএব $M = \frac{\mu_0 N_1 N_2 \pi r_1^2}{\ell}$। লক্ষণীয় যে ক্ষেত্রফল হিসেবে ক্ষুদ্রতর সলিনয়েডের ক্ষেত্রফল ($\pi r_1^2$) কার্যকর হয়।</t>
@@ -2820,11 +2665,6 @@
           <t>দুটি কুণ্ডলীর স্বকীয় আবেশ গুণাঙ্ক যথাক্রমে $L_1$ ও $L_2$ এবং তাদের মধ্যকার পারস্পরিক আবেশ গুণাঙ্ক $M$ হলে যুগলবন্দী বা কাপলিং সহগ (Coupling Coefficient, $k$)-এর সংজ্ঞা দাও এবং প্রমাণ করো যে তাত্ত্বিকভাবে $M \le \sqrt{L_1 L_2}$, অর্থাৎ $0 \le k \le 1$।</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>যুগল কুণ্ডলী ব্যবস্থায় মোট সঞ্চিত চৌম্বক শক্তি $U = \frac{1}{2} L_1 I_1^2 + \frac{1}{2} L_2 I_2^2 \pm M I_1 I_2$। যেহেতু চৌম্বক শক্তি একটি ভৌত বাস্তব রাশি, তাই যেকোনো কারেন্ট $I_1$ ও $I_2$-এর জন্য এর মান অবশ্যই অ-ঋণাত্মক হতে হবে ($U \ge 0$)। রাশিটিকে পূর্ণবর্গ আকারে সাজালে পাই: $U = \frac{1}{2}\left[\sqrt{L_1} I_1 \pm \frac{M}{\sqrt{L_1}} I_2\right]^2 + \frac{1}{2}\left[L_2 - \frac{M^2}{L_1}\right] I_2^2 \ge 0$। সমস্ত $I_2$-এর জন্য এই অসমতা সত্য হওয়ার একমাত্র শর্ত হলো: $L_2 - \frac{M^2}{L_1} \ge 0 \implies M^2 \le L_1 L_2 \implies M \le \sqrt{L_1 L_2}$। কাপলিং সহগ সংজ্ঞায়িত হয় $k \equiv \frac{M}{\sqrt{L_1 L_2}}$ দ্বারা। নিখুঁত চৌম্বক যুগলবন্দীতে (কোনো ফ্লাক্স লিকেজ না থাকলে) $k = 1$।</t>
@@ -2870,11 +2710,6 @@
           <t>$L_1$ ও $L_2$ স্বকীয় আবেশ এবং $M$ পারস্পরিক আবেশ বিশিষ্ট দুটি কুণ্ডলীকে শ্রেণীতে এমনভাবে যুক্ত করা হলো যাতে তাদের ফ্লাক্স (ক) একে অপরের সহায়ক হয় এবং (খ) একে অপরের বিরোধী হয়। উভয় ক্ষেত্রে তুল্য আবেশত্ব $L_{\text{eq}}$-এর রাশিমালা নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>শ্রেণী সমবায়ে উভয় কুণ্ডলীতে একই প্রবাহ $I$ থাকে এবং কারেন্ট পরিবর্তনের হার $\frac{dI}{dt}$ একই। ক) সহায়ক সমবায়ে (Aiding): উভয় কুণ্ডলীর নিজস্ব স্বকীয় ব্যাক-ইএমএফ এবং পারস্পরিক ব্যাক-ইএমএফ একই অভিমুখে যোগ হয়। প্রথম কুণ্ডলীর ভোল্টেজ $V_1 = L_1 \frac{dI}{dt} + M \frac{dI}{dt}$ এবং দ্বিতীয় কুণ্ডলীর ভোল্টেজ $V_2 = L_2 \frac{dI}{dt} + M \frac{dI}{dt}$। মোট ভোল্টেজ $V = V_1 + V_2 = (L_1 + L_2 + 2M)\frac{dI}{dt}$। তুল্য আবেশত্ব সমীকরণ $V = L_{\text{eq}}\frac{dI}{dt}$-এর সাথে তুলনা করলে পাই: $L_{\text{eq}} = L_1 + L_2 + 2M$। খ) বিরোধী সমবায়ে (Opposing): কুণ্ডলী দুটিতে কারেন্ট বিপরীত মুখে চলায় পারস্পরিক আবেশ স্বকীয় আবেশের বিরোধী হয়, ফলে মোট ভোল্টেজ $V = (L_1 + L_2 - 2M)\frac{dI}{dt} \implies L_{\text{eq}} = L_1 + L_2 - 2M$।</t>
@@ -2920,11 +2755,6 @@
           <t>প্রমাণ রোধ বাক্স (Resistance Box)-এর কুণ্ডলীগুলো তৈরিতে তারটিকে মাঝখান থেকে দ্বিগুণ ভাঁজ করে (Non-inductive winding) ববিনে পেঁচানো হয় কেন? এর স্বকীয় আবেশ কীভাবে শূন্য হয়?</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>একটি সাধারণ কুণ্ডলীতে কারেন্ট পাঠালে তার নিজস্ব স্বকীয় আবেশের কারণে পরিবর্তী প্রবাহে অতিরিক্ত আবেশীয় প্রতিঘাত $X_L = \omega L$ তৈরি হয় এবং ডিসি সুইচিংয়ে ট্রানজিয়েন্ট বিলম্ব ঘটে। রোধ বাক্সে বিশুদ্ধ ওহমীয় রোধ পেতে তারটিকে প্রথমে মাঝখানে ভাঁজ করে সমান্তরাল দ্বি-তার করা হয়। এরপর ববিনে পেঁচানো হয়। এর ফলে কুণ্ডলীর প্রতিটি পাকে কারেন্ট যেদিকে যায়, তার ঠিক পাশের তারটিতে কারেন্ট ঠিক বিপরীত দিকে ফিরে আসে। অ্যাম্পিয়ারের সূত্রানুযায়ী পাশাপাশি বিপরীতমুখী কারেন্টের সৃষ্টি চৌম্বক ক্ষেত্র সমান ও বিপরীত হওয়ায় নিট চৌম্বক ফ্লাক্স শূন্য হয় ($\Phi_{\text{net}} = \Phi - \Phi = 0$)। ফলে কুণ্ডলীর স্বকীয় আবেশত্ব প্রায় সম্পূর্ণ শূন্যে নেমে আসে।</t>
@@ -2970,11 +2800,6 @@
           <t>একই সমতলে সমকেন্দ্রে স্থাপিত দুটি বৃত্তাকার কুণ্ডলীর ব্যাসার্ধ যথাক্রমে $R$ এবং $r$ (যেখানে $R \gg r$) এবং তাদের পাকসংখ্যা যথাক্রমে $N_1$ ও $N_2$। কুণ্ডলীদ্বয়ের পারস্পরিক আবেশ গুণাঙ্ক $M$ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>বৃহৎ কুণ্ডলীটিতে (১) কারেন্ট $I_1$ প্রবাহিত করলে এর কেন্দ্রে সৃষ্ট চৌম্বক ক্ষেত্র $B_1 = \frac{\mu_0 N_1 I_1}{2 R}$। যেহেতু ক্ষুদ্র কুণ্ডলীর ব্যাসার্ধ অত্যন্ত ছোট ($r \ll R$), তাই ক্ষুদ্র কুণ্ডলীর সমগ্র ক্ষেত্রফল জুড়ে এই চৌম্বক ক্ষেত্রটিকে সুষম বিবেচনা করা যায়। ক্ষুদ্র কুণ্ডলীর একটি পাকের ফ্লাক্স $\Phi_2 = B_1 (\pi r^2) = \frac{\mu_0 N_1 I_1 \pi r^2}{2 R}$। ক্ষুদ্র কুণ্ডলীর সমস্ত $N_2$ টি পাকের মোট ফ্লাক্স लिंকেজ $\lambda_2 = N_2 \Phi_2 = \frac{\mu_0 \pi N_1 N_2 r^2}{2 R} I_1$। পারস্পরিক আবেশের সংজ্ঞামতে $\lambda_2 = M I_1$। অতএব $M = \frac{\mu_0 \pi N_1 N_2 r^2}{2 R}$।</t>
@@ -3020,11 +2845,6 @@
           <t>একটি বায়বীয় কোরের সলিনয়েডের ভেতর $\mu_r$ আপেক্ষিক প্রবেশ্যতার একটি নরম লোহার কোর সম্পূর্ণ প্রবিষ্ট করালে এর স্বকীয় আবেশ গুণাঙ্ক এবং সঞ্চিত শক্তির কী পরিবর্তন ঘটবে? লোহার কোরটি সম্পৃক্ত (saturated) হলে আবেশত্বের কী ঘটবে?</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>বায়বীয় কোরের স্বকীয় আবেশ $L_0 = \mu_0 n^2 A \ell$। লোহার কোর ঢোকালে মাধ্যমের প্রবেশ্যতা বৃদ্ধি পেয়ে হয় $\mu = \mu_r \mu_0$। ফলে নতুন আবেশত্ব $L = \mu_r L_0$। যেহেতু নরম লোহার $\mu_r \sim 1000 - 5000$, তাই আবেশত্ব কয়েক হাজার গুণ বৃদ্ধি পায়। তবে ফেরোচৌম্বক পদার্থের প্রবেশ্যতা ধ্রুবক নয়। যখন কারেন্ট অতিরিক্ত বৃদ্ধি পেয়ে কোরটি সম্পূর্ণ সম্পৃক্ততায় (magnetic saturation) পৌঁছায়, তখন নতুন কোনো ডোমেন সারিবদ্ধ হতে পারে না, ফলে $\frac{dB}{dI} \to \mu_0$ হয়। এর ফলে কুণ্ডলীর গতিশীল বা ডিফারেনশিয়াল আবেশত্ব $L_{\text{diff}} = \frac{d\lambda}{dI}$ আকস্মিকভাবে হ্রাস পেয়ে প্রায় শূন্যস্থান বা এয়ার-কোরের সমান হয়ে যায়।</t>
@@ -3070,11 +2890,6 @@
           <t>গড় ব্যাসার্ধ $R$, প্রস্থচ্ছেদ ক্ষেত্রফল $A$ এবং মোট পাকসংখ্যা $N$ বিশিষ্ট একটি টরয়েডাল কয়েলের স্বকীয় আবেশ গুণাঙ্ক $L$-এর সমীকরণ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>টরোয়েডে $I$ কারেন্ট প্রবাহিত হলে এর কোর বরাবর সুষম চৌম্বক ক্ষেত্র $B = \frac{\mu_0 N I}{2 \pi R}$। টরোয়েডের প্রস্থচ্ছেদ ক্ষেত্রফল $A$ হলে প্রতিটি পাকের চৌম্বক ফ্লাক্স $\Phi_B = B A = \frac{\mu_0 N I A}{2 \pi R}$। মোট $N$ টি পাকের সাথে জড়িত মোট ফ্লাক্স लिंকেজ $\lambda = N \Phi_B = \frac{\mu_0 N^2 A}{2 \pi R} I$। স্বকীয় আবেশের সংজ্ঞামতে $\lambda = L I$। অতএব টরোয়েডের স্বকীয় আবেশত্ব $L = \frac{\mu_0 N^2 A}{2 \pi R}$। যদি কোরে $\mu_r$ আপেক্ষিক প্রবেশ্যতার চৌম্বক উপাদান থাকে, তবে $L = \frac{\mu_0 \mu_r N^2 A}{2 \pi R}$।</t>
@@ -3120,11 +2935,6 @@
           <t>কোনো পারস্পরিক আবেশ নেই এমন দুটি কুণ্ডলী $L_1$ ও $L_2$ সমান্তরালে যুক্ত থাকলে তাদের তুল্য আবেশত্ব $L_{\text{eq}} = \frac{L_1 L_2}{L_1 + L_2}$ প্রতিপাদন করো।</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>সমান্তরাল সমবায়ে উভয় আবেশকের দুই প্রান্তের বিভব পার্থক্য $V$ সমান। প্রথম আবেশকে $V = L_1 \frac{dI_1}{dt} \implies \frac{dI_1}{dt} = \frac{V}{L_1}$। দ্বিতীয় আবেশকে $V = L_2 \frac{dI_2}{dt} \implies \frac{dI_2}{dt} = \frac{V}{L_2}$। বর্তনীর মোট প্রবাহ $I = I_1 + I_2$। সময় সাপেক্ষে ব্যবকলন করে: $\frac{dI}{dt} = \frac{dI_1}{dt} + \frac{dI_2}{dt} = \frac{V}{L_1} + \frac{V}{L_2} = V\left(\frac{1}{L_1} + \frac{1}{L_2}\right)$। তুল্য আবেশকের সমীকরণ $\frac{dI}{dt} = \frac{V}{L_{\text{eq}}}$-এর সাথে তুলনা করলে পাই: $\frac{1}{L_{\text{eq}}} = \frac{1}{L_1} + \frac{1}{L_2} \implies L_{\text{eq}} = \frac{L_1 L_2}{L_1 + L_2}$। এটি রোধের সমান্তরাল সমবায়ের হুবহু সমতুল্য।</t>
@@ -3170,11 +2980,6 @@
           <t>একটি বিশুদ্ধ আবেশক $L$ ও রোধক $R$ সম্বলিত বর্তনীতে একটি ডিসি ভোল্টেজ উৎস $\mathcal{E}$ যুক্ত করা হলো। সুইচ অন করার পর প্রবাহ বৃদ্ধির ক্ষণিক সমীকরণ $i(t)$ প্রতিপাদন করো। সময় ধ্রুবক $\tau = L/R$-এর সংজ্ঞা দাও।</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>কির্শফের ভোল্টেজ সূত্রানুযায়ী: $\mathcal{E} - L \frac{di}{dt} - i R = 0 \implies L \frac{di}{dt} + i R = \mathcal{E} \implies \frac{di}{\frac{\mathcal{E}}{R} - i} = \frac{R}{L} dt$। $t=0$-তে $i=0$ থেকে সমাকলন করে: $-\ln\left(\frac{\frac{\mathcal{E}}{R} - i}{\frac{\mathcal{E}}{R}}\right) = \frac{R t}{L} \implies 1 - \frac{i}{I_0} = e^{-Rt/L} \implies i(t) = I_0 (1 - e^{-t/\tau})$, যেখানে সর্বোচ্চ প্রবাহ $I_0 = \mathcal{E}/R$ এবং সময় ধ্রুবক $\tau = L/R$। $t = \tau$ বসালে: $i(\tau) = I_0 (1 - e^{-1}) \approx 0.632 I_0$। অর্থাৎ এক সময় ধ্রুবকে প্রবাহ তার চূড়ান্ত স্থির মানের ৬৩.২% বৃদ্ধি পায়।</t>
@@ -3220,11 +3025,6 @@
           <t>স্থায়ী প্রবাহ $I_0$ বিশিষ্ট একটি আর-এল বর্তনী থেকে ব্যাটারি বিচ্ছিন্ন করে বর্তনীটি শর্ট করে দিলে প্রবাহ ক্ষয়ের (decay of current) সমীকরণটি প্রতিষ্ঠা করো। কত সময় পর প্রবাহ তার প্রাথমিক মানের অর্ধেকের নেমে আসে?</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>ব্যাটারিহীন ক্ষয় লুপে KVL: $L \frac{di}{dt} + i R = 0 \implies \frac{di}{i} = -\frac{R}{L} dt$। $t=0$-তে $i=I_0$ থেকে সমাকলন করে: $\ln\left(\frac{i}{I_0}\right) = -\frac{R t}{L} \implies i(t) = I_0 e^{-t/\tau}$। যখন প্রবাহ অর্ধেক হয় ($i = I_0 / 2$): $\frac{I_0}{2} = I_0 e^{-t_{1/2}/\tau} \implies e^{t_{1/2}/\tau} = 2 \implies \frac{t_{1/2}}{\tau} = \ln 2 \implies t_{1/2} = \tau \ln 2 = \frac{L}{R} \ln 2 \approx 0.693 \frac{L}{R}$।</t>
@@ -3270,11 +3070,6 @@
           <t>একটি আবেশক $L$-এর মধ্য দিয়ে শূন্য থেকে $I$ পর্যন্ত কারেন্ট বৃদ্ধি করতে ব্যাক-ইএমএফের বিরুদ্ধে কৃতকাজের সমাকলন করে প্রমাণ করো যে আবেশকে সঞ্চিত চৌম্বক শক্তি $U = \frac{1}{2} L I^2$।</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>যেকোনো ক্ষণে আবেশকে ব্যাক-ইএমএফ $|\mathcal{E}| = L \frac{di}{dt}$। এই ব্যাক-ইএমএফের বিরুদ্ধে কারেন্ট বজায় রাখতে ব্যাটারি কর্তৃক সরবরাহকৃত তাৎক্ষণিক ক্ষমতা $P = |\mathcal{E}| i = \left(L \frac{di}{dt}\right) i$। $dt$ সময়ে ব্যাটারির কৃতকাজ $dW = P dt = L i di$। কারেন্ট শূন্য থেকে চূড়ান্ত মান $I$ পর্যন্ত বৃদ্ধি করতে মোট কৃতকাজ: $W = \int_0^I L i di = L \left[\frac{i^2}{2}\right]_0^I = \frac{1}{2} L I^2$। শক্তির সংরক্ষণশীলতা অনুসারে এই সম্পূর্ণ কাজটি আবেশকের চৌম্বক ক্ষেত্রে স্থিতিশক্তি রূপে জমা থাকে।</t>
@@ -3320,11 +3115,6 @@
           <t>দীর্ঘ সলিনয়েডের অভ্যন্তরীণ চৌম্বক ক্ষেত্র $B = \mu_0 n I$ এবং আবেশত্ব $L = \mu_0 n^2 A \ell$ ব্যবহার করে প্রতি একক আয়তনে সঞ্চিত চৌম্বক শক্তি ঘনত্ব $u_B = \frac{B^2}{2 \mu_0}$ প্রতিষ্ঠা করো। তড়িৎ ক্ষেত্রের শক্তি ঘনত্বের সাথে এর তুলনা করো।</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>সলিনয়েডে সঞ্চিত মোট শক্তি $U = \frac{1}{2} L I^2$। মান বসালে: $U = \frac{1}{2}(\mu_0 n^2 A \ell) I^2 = \frac{1}{2 \mu_0}(\mu_0 n I)^2 (A \ell)$। কিন্তু সলিনয়েডের অভ্যন্তরে ক্ষেত্র $B = \mu_0 n I$ এবং সলিনয়েডের মোট অভ্যন্তরীণ আয়তন $V = A \ell$। অতএব $U = \frac{B^2}{2 \mu_0} V$। প্রতি একক আয়তনে সঞ্চিত শক্তি বা শক্তি ঘনত্ব: $u_B = \frac{U}{V} = \frac{B^2}{2 \mu_0}$। এটি প্রমাণ করে যে চৌম্বক শক্তি তারের মধ্যে নয়, বরং তারের চারপাশের শূন্যস্থানে বিদ্যমান চৌম্বক ক্ষেত্রে ক্ষেত্র-ঘনত্ব আকারে সঞ্চিত থাকে।</t>
@@ -3370,11 +3160,6 @@
           <t>একটি উচ্চ আবেশক কুণ্ডলীর সুইচ হঠাৎ খুলে দিলে (অফ করলে) সুইচের দুই প্রান্তে তীব্র বৈদ্যুতিক স্ফুলিঙ্গ (inductive kickback) সৃষ্টি হয় কেন? রিলে ও মোটরের ট্রানজিস্টর ড্রাইভার সার্কিটকে সুরক্ষা দিতে ফ্লাইব্যাক ডায়োড কীভাবে কাজ করে?</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I46" t="inlineStr">
         <is>
           <t>সুইচ অন থাকা অবস্থায় আবেশকে কারেন্ট $I_0$ থাকে। সুইচটি হঠাৎ খুলে দিলে মাইক্রোসেকেন্ডের মধ্যে কারেন্ট শূন্য হতে চায় ($\Delta t \to 0$)। ফলে ব্যাক-ইএমএফ $\mathcal{E} = -L \frac{\Delta I}{\Delta t}$ সরবরাহ ভোল্টেজের তুলনায় শত শত গুণ বৃদ্ধি পেয়ে কয়েক হাজার ভোল্ট পর্যন্ত পৌঁছায়। এই অতিউচ্চ ভোল্টেজ সুইচের দুই প্রান্তের বায়ুর ডাই-ইলেকট্রিক ব্রেকডাউন ঘটিয়ে স্ফুলিঙ্গ তৈরি করে এবং সেমিকন্ডাক্টর ট্রানজিস্টর পুড়িয়ে ফেলে। কুণ্ডলীর সমান্তরালে বিপরীত পোলারিটিতে একটি 'ফ্লাইব্যাক ডায়োড' যুক্ত করা হয়। স্বাভাবিক অবস্থায় ডায়োডটি রিভার্স বায়াসে নিষ্ক্রিয় থাকে। কিন্তু সুইচ অফ করার মুহূর্তে আবেশকের উল্টে যাওয়া ব্যাক-ইএমএফ ডায়োডটিকে ফরওয়ার্ড বায়াস করে দেয়, ফলে কুণ্ডলীর কারেন্ট ডায়োডের মধ্য দিয়ে একটি বদ্ধ লুপে নিরাপদে নিজের অভ্যন্তরীণ রোধে তাপে ক্ষয়প্রাপ্ত হয়।</t>
@@ -3420,11 +3205,6 @@
           <t>স্থায়ী কারেন্ট $I_0$ বিশিষ্ট একটি আবেশক $L$-কে ব্যাটারি বিচ্ছিন্ন করে একটি রোধক $R$-এর মাধ্যমে সম্পূর্ণ ক্ষয় হতে দেওয়া হলো। সমাকলন পদ্ধতি ($\int_0^\infty i^2 R dt$) প্রয়োগ করে প্রমাণ করো যে রোধে উৎপন্ন মোট তাপশক্তি আবেশকে সঞ্চিত প্রাথমিক চৌম্বক শক্তির হুবহু সমান।</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I47" t="inlineStr">
         <is>
           <t>ক্ষয় কারেন্ট $i(t) = I_0 e^{-Rt/L}$। রোধে প্রতি সেকেন্ডে তাপ উৎপন্ন হওয়ার হার $P(t) = i^2 R = I_0^2 R e^{-2Rt/L}$। শূন্য থেকে অসীম সময় পর্যন্ত মোট উৎপন্ন তাপশক্তি: $H = \int_0^\infty P(t) dt = I_0^2 R \int_0^\infty e^{-2Rt/L} dt = I_0^2 R \left[-\frac{L}{2R} e^{-2Rt/L}\right]_0^\infty = I_0^2 R \left(0 - \left(-\frac{L}{2R}\right)\right) = \frac{1}{2} L I_0^2$। এই ফলাফল প্রমাণ করে যে কোনো অতিরিক্ত শক্তি অপচয় বা সৃষ্টি ছাড়াই আবেশকে সঞ্চিত প্রাথমিক চৌম্বক শক্তি $\frac{1}{2} L I_0^2$ হুবহু সম্পূর্ণভাবে রোধে তাপশক্তিতে রূপান্তরিত হয়।</t>
@@ -3470,11 +3250,6 @@
           <t>$Q_0$ আধানে আহিত একটি আদর্শ ধারক $C$-কে একটি বিশুদ্ধ আবেশক $L$-এর সাথে যুক্ত করে বর্তনীটি বন্ধ করা হলো। আধান ও প্রবাহের দ্বিতীয় ক্রমের ব্যবকলন সমীকরণ প্রতিষ্ঠা করো এবং আধানের মুক্ত দোলনের কম্পাঙ্ক $f_0$ নির্ণয় করো।</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>বর্তনীতে কোনো রোধ না থাকায় KVL: $\frac{q}{C} + L \frac{di}{dt} = 0$। যেহেতু কারেন্ট আধান ক্ষরণের হার, তাই $i = \frac{dq}{dt} \implies \frac{di}{dt} = \frac{d^2 q}{dt^2}$। মান বসালে: $L \frac{d^2 q}{dt^2} + \frac{q}{C} = 0 \implies \frac{d^2 q}{dt^2} + \left(\frac{1}{LC}\right) q = 0$। এটি সরল ছন্দিত স্পন্দনের আদর্শ সমীকরণ ($\ddot{x} + \omega_0^2 x = 0$), যেখানে স্বাভাবিক কৌণিক কম্পাঙ্ক $\omega_0 = \frac{1}{\sqrt{LC}}$। অতএব দোলনের কম্পাঙ্ক $f_0 = \frac{\omega_0}{2\pi} = \frac{1}{2\pi \sqrt{LC}}$। আধান $q(t) = Q_0 \cos(\omega_0 t)$ অনুসারে স্পন্দিত হয় এবং শক্তি ধারকের স্থিরতড়িৎ ক্ষেত্র ($U_E = \frac{q^2}{2C}$) ও আবেশকের চৌম্বক ক্ষেত্রের ($U_B = \frac{1}{2} L i^2$) মধ্যে অবিরত রূপান্তরিত হতে থাকে।</t>
@@ -3520,11 +3295,6 @@
           <t>$\mathcal{E}$ ভোল্টেজের ব্যাটারির সাথে একটি রোধ $R$ ও আবেশক $L$ শ্রেণীতে যুক্ত। সুইচ বন্ধ করার ঠিক তাৎক্ষণিক মুহূর্তে ($t = 0^+$) আবেশকের দুই প্রান্তের বিভব পার্থক্য কত এবং রোধের দুই প্রান্তের বিভব পার্থক্য কত?</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>আবেশকের মধ্য দিয়ে কারেন্ট তাৎক্ষণিকভাবে লাফ দিয়ে পরিবর্তিত হতে পারে না ($i(0^+) = i(0^-) = 0$)। ফলে সুইচ অন করার তাৎক্ষণিক মুহূর্তে বর্তনীতে কারেন্ট শূন্য থাকে ($i = 0$)। ওহমের সূত্রানুযায়ী রোধের দুই প্রান্তের বিভব পতন $V_R = i R = 0$। KVL সমীকরণ $\mathcal{E} - V_R - V_L = 0$ বসালে পাই: $V_L = \mathcal{E} - 0 = \mathcal{E}$। অর্থাৎ সুইচ অনের ঠিক শুরুতে সরবরাহকৃত সম্পূর্ণ ভোল্টেজটিই আবেশকের দুই প্রান্তে ব্যাক-ইএমএফ হিসেবে আবির্ভূত হয় এবং আবেশকটি একটি উন্মুক্ত বর্তনীর (open circuit) ন্যায় আচরণ করে।</t>
@@ -3570,11 +3340,6 @@
           <t>বিদ্যুৎ গ্রিডের স্থিতিশীলতা রক্ষায় ব্যবহৃত এসএমইএস (SMES - Superconducting Magnetic Energy Storage) ব্যবস্থায় কোনো শক্তি অপচয় ছাড়াই দীর্ঘকাল বিপুল পরিমাণ বৈদ্যুতিক শক্তি কীভাবে সংরক্ষণ করা হয়?</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I50" t="inlineStr">
         <is>
           <t>প্রথাগত ব্যাটারিতে রাসায়নিক শক্তির রূপান্তরের কারণে শক্তির অপচয় ও সীমিত জীবনকাল থাকে। এসএমইএস-এ নিওবিয়াম-টাইটানিয়াম বা উচ্চ তাপমাত্রার সুপারকন্ডাক্টিং কয়েল তরল হিলিয়াম বা নাইট্রোজেনে ডুবিয়ে রাখা হয় যার রোধ নিখুঁত শূন্য ($R=0$)। গ্রিডের অতিরিক্ত বিদ্যুৎ দিয়ে কয়েলটিতে হাজার হাজার অ্যাম্পিয়ার কারেন্ট প্রবেশ করিয়ে কয়েলটির দুই প্রান্ত শর্ট করে দেওয়া হয়। যেহেতু রোধ শূন্য, তাই জুল তাপন অপচয় $I^2 R = 0$। ফলে কারেন্ট কোনো ক্ষয় ছাড়াই অনন্তকাল ধরে অবিরাম ঘুরতে থাকে এবং কয়েলের তীব্র চৌম্বক ক্ষেত্রে মেগাওয়াট স্তরের শক্তি জমা থাকে। গ্রিডে আকস্মিক লোড বাড়লে ইনভার্টারের মাধ্যমে মিলি-সেকেন্ডের মধ্যে এই সঞ্চিত চৌম্বক শক্তিকে পুনরায় এসি বিদ্যুতে রূপান্তর করে গ্রিডে সরবরাহ করা হয়।</t>
@@ -3620,11 +3385,6 @@
           <t>একটি আর-এল বর্তনীতে একটি ব্যাটারির সাহায্যে কারেন্ট $I_0$-তে উন্নীত করার পর একটি চাবির সাহায্যে ব্যাটারিটিকে বিচ্ছিন্ন করে তাৎক্ষণিকভাবে একটি অতিরিক্ত রোধ $R_2$ যুক্ত করা হলো। চাবি পরিবর্তনের ঠিক পরবর্তী মুহূর্তে আবেশকের দুই প্রান্তের বিভব পার্থক্য কত হবে এবং এর চিহ্ন কী হবে?</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>সুইচ পরিবর্তনের ঠিক পূর্বে আবেশকের মধ্য দিয়ে কারেন্ট ছিল $I_0$। আবেশকের অন্তর্নিহিত বৈশিষ্ট্যের কারণে সুইচ পরিবর্তনের ঠিক তাৎক্ষণিক মুহূর্তেও কারেন্ট অপরিবর্তিত থাকে: $i(0^+) = I_0$। কিন্তু এখন বর্তনীর মোট রোধ বেড়ে হয়েছে $R_{\text{new}} = R + R_2$। KVL সমীকরণ: $V_L + i(R + R_2) = 0 \implies V_L = -I_0 (R + R_2)$। যদি $R_2 \gg R$ হয়, তবে আবেশকের দুই প্রান্তে মূল ব্যাটারির চেয়ে বহুগুণ শক্তিশালী ঋণাত্মক ভোল্টেজ স্পাইক আবির্ভূত হয়। এই প্রক্রিয়াকে ব্যবহার করে অটোমোবাইলের ইগনিশন কয়েলে ১২ ভোল্ট ব্যাটারি থেকে ২০,০০০ ভোল্টের স্পার্ক তৈরি করে ইঞ্জিনের জ্বালানি প্রজ্বলন করা হয়।</t>
@@ -3654,7 +3414,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা (সমস্যা 1)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -3663,35 +3423,29 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##
-[সমস্যা 1: শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা]
-##PRESET:circuit-ac[size:medium]##
-একটি শ্রেণি RLC বর্তনীতে $R = 40\ \Omega$, $L = 0.3\text{ H}$ এবং $C = 10\ \mu\text{F}$ যুক্ত করে $V = 220\text{ V}$ পরিবর্তী উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর অনুনাদী কম্পাঙ্ক ($f_0$) এবং অনুনাদ অবস্থায় শীর্ষ প্রবাহ নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $N = 200$ পাকের কুণ্ডলীর ক্ষেত্রফল $A = 0.05\text{ m}^2$। কুণ্ডলীটি একটি চৌম্বক ক্ষেত্রের সাথে লম্বভাবে অবস্থিত। চৌম্বক ক্ষেত্র $0.10\text{ সেকেন্ডে}$ সুষম হারে $0.20\text{ T}$ হতে বৃদ্ধি পেয়ে $0.80\text{ T}$ হলে কুণ্ডলীতে আবিষ্ট তড়িচ্চালক বল $\mathcal{E}$ নির্ণয় কর। কুণ্ডলীর রোধ $4.0\text{ }\Omega$ হলে আবিষ্ট তড়িৎ প্রবাহ কত?</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 1)।</t>
+          <t>ফ্লাক্স পরিবর্তন $\Delta\Phi = A \Delta B = 0.05 \times (0.80 - 0.20) = 0.05 \times 0.60 = 0.030\text{ Wb}$। ফ্যারাডের সূত্রানুযায়ী আবিষ্ট $\text{EMF} \mathcal{E} = N \frac{\Delta\Phi}{\Delta t} = 200 \times \frac{0.030}{0.10} = 200 \times 0.30 = 60.0\text{ V}$। আবিষ্ট কারেন্ট $I = \frac{\mathcal{E}}{R} = \frac{60.0\text{ V}}{4.0\text{ }\Omega} = 15.0\text{ A}$।</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} \mathcal{E} = 60.0\text{ V}$, আবিষ্ট কারেন্ট $I = 15.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3711,12 +3465,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ (সমস্যা 2)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -3724,31 +3478,25 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##
-[সমস্যা 2: স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ]
-##PRESET:transformer[size:medium]##
-একটি আদর্শ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 600$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 50$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করলে গৌণ কুণ্ডলীর প্রান্তীয় ভোল্টেজ এবং মুখ্য প্রবাহ $1\text{ A}$ হলে গৌণ প্রবাহ কত?</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি $L = 1.0\text{ m}$ দৈর্ঘ্যের ধাতব রড $B = 0.40\text{ T}$ সুষম চৌম্বক ক্ষেত্রের লম্বতলে এক প্রান্তকে কেন্দ্র করে $\omega = 20.0\text{ rad/s}$ সমকৌণিক বেগে ঘুরছে। রডের দুই প্রান্তের মধ্যে আবিষ্ট তড়িচ্চালক বল কত?</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 2)।</t>
+          <t>আবর্তিত রডের দুই প্রান্তের আবিষ্ট $\text{EMF}: \mathcal{E} = \frac{1}{2} B \omega L^2 = \frac{1}{2} \times 0.40 \times 20.0 \times (1.0)^2 = 0.20 \times 20.0 = 4.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 2</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} \mathcal{E} = 4.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3768,7 +3516,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল (সমস্যা 3)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3777,29 +3525,29 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>[সমস্যা 3: ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল]
-একটি $N = 800$ পাকের কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স $\Delta t = 0.7\text{ s}$-এ $0.08\text{ Wb}$ হতে $0.02\text{ Wb}$-এ হ্রাস পেল। কুণ্ডলীতে আবিষ্ট গড় তড়িচ্চালক বল ($e = -N\frac{\Delta\Phi}{\Delta t}$) কত ভোল্ট?</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2][size:small]##
+একটি উড়োজাহাজের ডানার বিস্তার (Wingspan) $L = 40.0\text{ m}$। বিমানটি $v = 720\text{ km/h}$ অনুভূমিক বেগে উত্তর দিকে উড়ে যাচ্ছে। ওই স্থানে ভূ-চৌম্বক ক্ষেত্রের উল্লম্ব উপাংশ $B_V = 3.0 \times 10^{-5}\text{ T}$ হলে ডানার দুই প্রান্তের মধ্যে উৎপন্ন বিভব পার্থক্য কত?</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 3)।</t>
+          <t>বেগ $v = \frac{720 \times 1000}{3600} = 200.0\text{ m/s}$। ডানা অনুভূমিকভাবে চলার সময় ভূ-চৌম্বক ক্ষেত্রের উল্লম্ব উপাংশকে লম্বভাবে ছেদ করে। আবিষ্ট $\text{EMF}: \mathcal{E} = B_V v L = (3.0 \times 10^{-5}\text{ T}) \times (200.0\text{ m/s}) \times (40.0\text{ m}) = 0.240\text{ V} = 240.0\text{ mV}$।</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 3</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>বিভব পার্থক্য $\mathcal{E} = 0.240\text{ V} = 240.0\text{ mV}$</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3819,12 +3567,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ (সমস্যা 4)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -3832,25 +3580,25 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>[সমস্যা 4: ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ]
-$L = 1.0\text{ m}$ দীর্ঘ একটি ধাতব পরিবাহী দণ্ড $B = 0.10\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে এক প্রান্তকে কেন্দ্র করে $\omega = 90\text{ rad/s}$ কৌণিক দ্রুতিতে ঘুরছে। দণ্ডের দুই প্রান্তের মধ্যে আবিষ্ট বিভব পার্থক্য ($e = \frac{1}{2}B\omega L^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি কুণ্ডলীর স্বকীয় আবেশ গুণাঙ্ক (Self-inductance) $L = 0.50\text{ H}$। কুণ্ডলীতে তড়িৎ প্রবাহ $0.05\text{ সেকেন্ডে}$ সুষম হারে $10.0\text{ A}$ হতে হ্রাস পেয়ে শূন্যে নেমে এলে আবিষ্ট তড়িচ্চালক বলের মান কত?</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 4)।</t>
+          <t>আবিষ্ট $\text{EMF}: \mathcal{E} = -L \frac{\Delta I}{\Delta t} = -(0.50) \times \frac{0 - 10.0}{0.05} = -(0.50) \times (-200) = 100.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 4</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} \mathcal{E} = 100.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3870,7 +3618,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি (সমস্যা 5)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3879,29 +3627,29 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>[সমস্যা 5: স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি]
-একটি কুণ্ডলীর স্বকীয় আবেশাঙ্ক $L = 12.0\text{ H}$। এর মধ্য দিয়ে বিদ্যুৎ প্রবাহ $0.1\text{ s}$ সময়ে $1\text{ A}$ হতে শূন্যে নেমে এলে আবিষ্ট ইএমএফ এবং প্রাথমিক অবস্থায় সঞ্চিত শক্তি ($U = \frac{1}{2}LI^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##
+একটি সলিনয়েডের দৈর্ঘ্য $l = 40.0\text{ cm}$, ব্যাসার্ধ $r = 2.0\text{ cm}$ এবং মোট পাকসংখ্যা $N = 800$। সলিনয়েডটির স্ববেশাঙ্ক (Self-inductance $L$) কত মিলি-হেনরি? এতে $I = 3.0\text{ A}$ কারেন্ট চললে সঞ্চিত চৌম্বক শক্তি $U_B$ কত?</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=4][size:small]##</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 5)।</t>
+          <t>প্রস্থচ্ছেদের ক্ষেত্রফল $A = \pi r^2 = \pi (0.02)^2 = 4\pi \times 10^{-4}\text{ m}^2 \approx 1.2566 \times 10^{-3}\text{ m}^2$। সলিনয়েডের স্ববেশাঙ্ক $L = \frac{\mu_0 N^2 A}{l} = \frac{(4\pi \times 10^{-7}) \times 800^2 \times (1.2566 \times 10^{-3})}{0.40} = \frac{1.0106 \times 10^{-3}}{0.40} \approx 2.5266 \times 10^{-3}\text{ H} \approx 2.53\text{ mH}$। সঞ্চিত চৌম্বক শক্তি $U_B = \frac{1}{2} L I^2 = \frac{1}{2}(2.5266 \times 10^{-3})(3.0)^2 = 0.5 \times 2.5266 \times 10^{-3} \times 9 \approx 0.01137\text{ J} = 11.37\text{ mJ}$।</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 5</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
+          <t>স্ববেশাঙ্ক $L = 2.53\text{ mH}$, সঞ্চিত শক্তি $U_B = 0.01138\text{ J} = 11.38\text{ mJ}$</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3921,12 +3669,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ (সমস্যা 6)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -3934,25 +3682,25 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>[সমস্যা 6: পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ]
-দুটি পাশাপাশি রাখা কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক $M = 0.2\text{ H}$। মুখ্য কুণ্ডলীতে প্রবাহ $\Delta t = 0.05\text{ s}$-এ শূন্য হতে $3\text{ A}$-তে উন্নীত করলে গৌণ কুণ্ডলীতে আবিষ্ট ইএমএফ কত?</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+দুটি কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক (Mutual inductance) $M = 1.5\text{ H}$। প্রাথমিক কুণ্ডলীতে কারেন্ট পরিবর্তনের হার $rac{dI}{dt} = 40.0\text{ A/s}$ হলে গৌণ কুণ্ডলীতে আবিষ্ট তড়িচ্চালক বল কত?</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 6)।</t>
+          <t>পারস্পরিক আবেশের সূত্র: $\mathcal{E}_2 = M \frac{dI_1}{dt} = 1.5\text{ H} \times 40.0\text{ A/s} = 60.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} \mathcal{E}_2 = 60.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3972,7 +3720,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান (সমস্যা 7)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3981,29 +3729,29 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>[সমস্যা 7: পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান]
-একটি সাইনুসয়েডাল পরিবর্তী ভোল্টেজের সমীকরণ $V(t) = 400 \sin(500\pi t)\text{ V}$। উৎসটির শীর্ষ ভোল্টেজ ($V_0$), কার্যকর ভোল্টেজ ($V_{rms}$) এবং কম্পাঙ্ক ($f$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+লেনজের সূত্রটি বিবৃত কর এবং দেখাও যে এটি শক্তির সংরক্ষণশীলতা নীতির একটি প্রত্যক্ষ পরিণতি।</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 7)।</t>
+          <t>চৌম্বক মেরুকে কুণ্ডলীর দিকে আনলে বিকর্ষণ বল সৃষ্টি হয় এবং দূরে নিলে আকর্ষণ বল সৃষ্টি হয়। ফলে উভয় ক্ষেত্রেই চুম্বকটিকে সরাতে বাহ্যিক যান্ত্রিক কাজ সম্পাদন করতে হয়। এই যান্ত্রিক কাজের সমপরিমাণ শক্তি কুণ্ডলীতে বৈদ্যুতিক শক্তি ও তাপে রূপান্তরিত হয়। কোনো শক্তি শূন্য থেকে সৃষ্টি হয় না, যা শক্তির সংরক্ষণশীলতাকে সমর্থন করে।</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 7</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+          <t>আবিষ্ট তড়িচ্চালক বলের অভিমুখ এমন হয় যেন এটি সৃষ্টির মূল কারণকে বাধা প্রদান করে; বাহ্যিক বাধার বিরুদ্ধে কৃতকাজই বৈদ্যুতিক শক্তিতে রূপান্তরিত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4023,12 +3771,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত (সমস্যা 8)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -4036,25 +3784,25 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>[সমস্যা 8: আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত]
-একটি $L = 0.6\text{ H}$ আবেশকের মধ্য দিয়ে $f = 50\text{ Hz}$ কম্পাঙ্কের পরিবর্তী প্রবাহ চলছে। আবেশকটির আবেশীয় প্রতিঘাত ($X_L = 2\pi f L$) কত ওহম?</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স সময়ের সাথে পরিবর্তিত হয়: $\Phi(t) = 6t^2 + 7t + 2\text{ Wb}$। $t = 2.0\text{ সেকেন্ড}$ মুহূর্তে কুণ্ডলীতে আবিষ্ট তড়িচ্চালক বলের মান কত?</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 8)।</t>
+          <t>$\mathcal{E} = -\frac{d\Phi}{dt} = -\frac{d}{dt}(6t^2 + 7t + 2) = -(12t + 7)$। $t = 2.0\text{ s}$ মুহূর্তে: $\mathcal{E} = -(12(2) + 7) = -(24 + 7) = -31.0\text{ V}$। মান $= 31.0\text{ V}$।</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 8</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} |\mathcal{E}| = 31.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4074,7 +3822,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>বর্তনীর ক্ষমতা গুণক (Power Factor) (সমস্যা 9)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4083,29 +3831,29 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>[সমস্যা 9: বর্তনীর ক্ষমতা গুণক (Power Factor)]
-একটি পরিবর্তী বর্তনীতে রোধ $R = 80\ \Omega$ এবং মোট প্রতিবন্ধকতা $Z = 90\ \Omega$। বর্তনীর ক্ষমতা গুণক ($\\cos\phi = R/Z$) কত এবং $V_{rms} = 220\text{ V}$ হলে ব্যয়িত গড় ক্ষমতা কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি তারের তৈরি $A = 0.10\text{ m}^2$ ক্ষেত্রফল ও $R = 2.0\text{ }\Omega$ রোধের বর্গাকার লুপ একটি সুষম চৌম্বক ক্ষেত্র $B = 0.50\text{ T}$-এ লম্বভাবে স্থাপিত। লুপটিকে হঠাৎ টেনে $0.05\text{ সেকেন্ডে}$ সম্পূর্ণ বাইরে বের করে নেওয়া হলে লুপের মধ্য দিয়ে প্রবাহিত মোট আধান $Q$ কত কুলম্ব?</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 9)।</t>
+          <t>ফ্লাক্স পরিবর্তন $\Delta\Phi = B A - 0 = 0.50 \times 0.10 = 0.050\text{ Wb}$। প্রবাহিত মোট আধান সময় নিরপেক্ষ: $Q = \frac{\Delta\Phi}{R} = \frac{0.050\text{ Wb}}{2.0\text{ }\Omega} = 0.025\text{ C} = 25.0\text{ mC}$।</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 9</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>মোট আধান $Q = 0.025\text{ C} = 25.0\text{ mC}$</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4125,12 +3873,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ (সমস্যা 10)</t>
+          <t>তাড়িতচৌম্বক আবেশ, স্ববেশাঙ্ক ও ফ্যারাডের সূত্র (Electromagnetic Induction)</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -4138,25 +3886,25 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>[সমস্যা 10: ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ]
-একটি আয়তাকার কুণ্ডলী $N = 1000$ পাক এবং ক্ষেত্রফল $A = 0.01\text{ m}^2$। এটি $B = 0.5\text{ T}$ চৌম্বক ক্ষেত্রে $\omega = 100\pi\text{ rad/s}$ বেগে ঘুরলে সর্বোচ্চ আবিষ্ট ভোল্টেজ ($e_0 = NAB\omega$) কত?</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+ঘূর্ণি প্রবাহ (Eddy currents / Foucault currents) বলতে কী বোঝায়? ট্রান্সফরমারের কোরে এই অপচয় রোধ করতে কোরকে কীভাবে প্রস্তুত করা হয়?</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 10)।</t>
+          <t>ধাতব খণ্ডের মধ্য দিয়ে ফ্লাক্স পরিবর্তিত হলে ধাতুটির ভেতর অসংখ্য আবদ্ধ স্থানীয় ঘূর্ণিপথে কারেন্ট ঘোরে, যার ফলে অতিরিক্ত জুল তাপ অপচয় ঘটে। এই অপচয় কমাতে ট্রান্সফরমার বা মোটরের কোরকে একটি নিরেট ব্লকের পরিবর্তে বার্নিশ বা ইনসুলেটিং আস্তরণযুক্ত পাতলা পাতলা স্তরায়িত শিট (Laminated core) জোড়া লাগিয়ে তৈরি করা হয় যাতে ঘূর্ণি প্রবাহের পথ বাধাপ্রাপ্ত ও দীর্ঘায়িত হয়।</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 10</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
+          <t>পরিবর্তনশীল চৌম্বক ক্ষেত্রে ধাতব ব্লকে আবিষ্ট স্থানীয় আবদ্ধ তড়িৎ প্রবাহ; পাতলা স্তরায়িত ল্যামিনেশন (Laminated sheets) ব্যবহার করে রোধ করা হয়</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4176,44 +3924,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা (সমস্যা 11)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##
-[সমস্যা 11: শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা]
-##PRESET:circuit-ac[size:medium]##
-একটি শ্রেণি RLC বর্তনীতে $R = 120\ \Omega$, $L = 0.3\text{ H}$ এবং $C = 10\ \mu\text{F}$ যুক্ত করে $V = 220\text{ V}$ পরিবর্তী উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর অনুনাদী কম্পাঙ্ক ($f_0$) এবং অনুনাদ অবস্থায় শীর্ষ প্রবাহ নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরিবর্তী প্রবাহের সমীকরণ $I(t) = 10\sqrt{2}\sin(100\pi t)$ অ্যাম্পিয়ার। প্রবাহটির শীর্ষ মান $I_0$, কার্যকর মান (RMS মান $I_{	ext{rms}}$), পর্যায়কাল $T$ এবং কম্পাঙ্ক $f$ নির্ণয় কর। $t = rac{1}{600}\text{ সেকেন্ড}$ মুহূর্তে প্রবাহের তাৎক্ষণিক মান কত?</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 11)।</t>
+          <t>শীর্ষ মান $I_0 = 10\sqrt{2} \approx 14.14\text{ A}$। RMS মান $I_{\text{rms}} = \frac{I_0}{\sqrt{2}} = 10.0\text{ A}$। কৌণিক কম্পাঙ্ক $\omega = 100\pi \implies 2\pi f = 100\pi \implies f = 50.0\text{ Hz}$। পর্যায়কাল $T = 1/50 = 0.02\text{ s}$। $t = 1/600\text{ s}$-এ দশা $\Phi = 100\pi \times \frac{1}{600} = \frac{\pi}{6} = 30^\circ$। তাৎক্ষণিক প্রবাহ $I = 10\sqrt{2}\sin(30^\circ) = 10\sqrt{2}(0.5) = 5\sqrt{2} \approx 7.071\text{ A}$।</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 11</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+          <t>$I_0 = 14.14\text{ A}, I_{\text{rms}} = 10.0\text{ A}, f = 50.0\text{ Hz}, T = 0.02\text{ s}$, তাৎক্ষণিক মান $I = 7.07\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4233,7 +3975,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ (সমস্যা 12)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4246,31 +3988,25 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##
-[সমস্যা 12: স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ]
-##PRESET:transformer[size:medium]##
-একটি আদর্শ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 200$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 50$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করলে গৌণ কুণ্ডলীর প্রান্তীয় ভোল্টেজ এবং মুখ্য প্রবাহ $1\text{ A}$ হলে গৌণ প্রবাহ কত?</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+বাংলাদেশের গৃহস্থালি বিদ্যুৎ লাইনের ভোল্টেজ $220\text{ V}, 50\text{ Hz}$। এই ভোল্টেজের শীর্ষ মান (Peak voltage $V_0$) কত এবং এর পূর্ণ চক্রের গড় মান কত?</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 12)।</t>
+          <t>সরবরাহকৃত $220\text{ V}$ হলো RMS ভোল্টেজ: $V_{\text{rms}} = 220\text{ V}$। শীর্ষ ভোল্টেজ $V_0 = \sqrt{2} V_{\text{rms}} = 1.4142 \times 220 \approx 311.13\text{ V}$। একটি পূর্ণ চক্রে ধনাত্মক ও ঋণাত্মক অর্ধচক্র সমান ও বিপরীতমুখী হওয়ায় পূর্ণ চক্রের গড় মান শূন্য।</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 12</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
+          <t>শীর্ষ ভোল্টেজ $V_0 = 311.13\text{ V}$, পূর্ণ চক্রে গড় ভোল্টেজ $= 0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4290,38 +4026,38 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল (সমস্যা 13)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>[সমস্যা 13: ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল]
-একটি $N = 400$ পাকের কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স $\Delta t = 0.7\text{ s}$-এ $0.08\text{ Wb}$ হতে $0.02\text{ Wb}$-এ হ্রাস পেল। কুণ্ডলীতে আবিষ্ট গড় তড়িচ্চালক বল ($e = -N\frac{\Delta\Phi}{\Delta t}$) কত ভোল্ট?</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি খাঁটি আবেশকের আবেশাঙ্ক $L = 0.20\text{ H}$। এটিকে $220\text{ V}, 50\text{ Hz}$ এসি উৎসের সাথে যুক্ত করা হলো। কুণ্ডলীর আবেশীয় ঘাত (Inductive reactance $X_L$) এবং বর্তনীর RMS প্রবাহ কত?</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 13)।</t>
+          <t>কৌণিক কম্পাঙ্ক $\omega = 2\pi f = 2\pi(50) = 100\pi \approx 314.16\text{ rad/s}$। আবেশীয় ঘাত $X_L = \omega L = 100\pi \times 0.20 = 20\pi \approx 62.83\text{ }\Omega$। বর্তনীর প্রবাহ $I_{\text{rms}} = \frac{V_{\text{rms}}}{X_L} = \frac{220}{62.83} \approx 3.501\text{ A}$।</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 13</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
+          <t>আবেশীয় ঘাত $X_L = 62.83\text{ }\Omega$, প্রবাহ $I = 3.50\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4341,7 +4077,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ (সমস্যা 14)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4354,25 +4090,25 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>[সমস্যা 14: ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ]
-$L = 1.0\text{ m}$ দীর্ঘ একটি ধাতব পরিবাহী দণ্ড $B = 0.6\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে এক প্রান্তকে কেন্দ্র করে $\omega = 90\text{ rad/s}$ কৌণিক দ্রুতিতে ঘুরছে। দণ্ডের দুই প্রান্তের মধ্যে আবিষ্ট বিভব পার্থক্য ($e = \frac{1}{2}B\omega L^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2][size:small]##
+একটি $C = 20.0\text{ }\mu	ext{F}$ ধারককে $110\text{ V}, 50\text{ Hz}$ এসি মেইন্সে সংযোগ দেওয়া হলো। ধারকীয় ঘাত (Capacitive reactance $X_C$) এবং বর্তনীর কারেন্ট নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2][size:small]##</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 14)।</t>
+          <t>ধারকীয় ঘাত $X_C = \frac{1}{\omega C} = \frac{1}{2\pi f C} = \frac{1}{2\pi (50)(20 \times 10^{-6})} = \frac{10^6}{2000\pi} = \frac{500}{\pi} \approx 159.155\text{ }\Omega$। প্রবাহ $I_{\text{rms}} = \frac{V}{X_C} = \frac{110}{159.155} \approx 0.6912\text{ A}$।</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 14</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+          <t>ধারকীয় ঘাত $X_C = 159.15\text{ }\Omega$, প্রবাহ $I = 0.691\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4392,38 +4128,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি (সমস্যা 15)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>[সমস্যা 15: স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি]
-একটি কুণ্ডলীর স্বকীয় আবেশাঙ্ক $L = 8.0\text{ H}$। এর মধ্য দিয়ে বিদ্যুৎ প্রবাহ $0.1\text{ s}$ সময়ে $1\text{ A}$ হতে শূন্যে নেমে এলে আবিষ্ট ইএমএফ এবং প্রাথমিক অবস্থায় সঞ্চিত শক্তি ($U = \frac{1}{2}LI^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি রোধক $R = 40.0\text{ }\Omega$ এবং একটি ধারক $C = 100.0\text{ }\mu	ext{F}$ শ্রেণিতে যুক্ত করে $200\text{ V}, 50\text{ Hz}$ উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর মোট প্রতিবন্ধকতা (Impedance $Z$), প্রবাহ $I$ এবং ভোল্টেজ ও প্রবাহের মধ্যকার দশা কোণ $\phi$ কত?</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 15)।</t>
+          <t>$X_C = \frac{1}{2\pi (50)(100 \times 10^{-6})} = \frac{10^4}{100\pi} = \frac{100}{\pi} \approx 31.83\text{ }\Omega$। প্রতিবন্ধকতা $Z = \sqrt{R^2 + X_C^2} = \sqrt{40^2 + 31.83^2} = \sqrt{1600 + 1013.15} = \sqrt{2613.15} \approx 51.07\text{ }\Omega$। প্রবাহ $I = \frac{V}{Z} = \frac{200}{51.07} \approx 3.916\text{ A}$। দশা কোণ $\tan\phi = \frac{X_C}{R} = \frac{31.83}{40} \approx 0.7958 \implies \phi \approx 38.51^\circ$ (ধারকীয় বর্তনী হওয়ায় প্রবাহ ভোল্টেজ অপেক্ষা অগ্রগামী)।</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 15</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
+          <t>প্রতিবন্ধকতা $Z = 51.07\text{ }\Omega$, প্রবাহ $I = 3.916\text{ A}$, দশা কোণ $\phi = 38.51^\circ$ (প্রবাহ অগ্রগামী)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4443,7 +4179,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ (সমস্যা 16)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -4456,25 +4192,25 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>[সমস্যা 16: পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ]
-দুটি পাশাপাশি রাখা কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক $M = 0.10\text{ H}$। মুখ্য কুণ্ডলীতে প্রবাহ $\Delta t = 0.05\text{ s}$-এ শূন্য হতে $3\text{ A}$-তে উন্নীত করলে গৌণ কুণ্ডলীতে আবিষ্ট ইএমএফ কত?</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $R = 30.0\text{ }\Omega$ রোধক এবং $L = 0.127\text{ H}$ আবেশক শ্রেণিতে যুক্ত করে $220\text{ V}, 50\text{ Hz}$ লাইনে সংযোগ দেওয়া হলো। বর্তনীর ক্ষমতা গুণক (Power factor $\cos\phi$) এবং গড় ক্ষমতা ব্যয় $P$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 16)।</t>
+          <t>$X_L = 2\pi f L = 2\pi(50)(0.127) = 100\pi(0.127) \approx 39.90\text{ }\Omega \approx 40.0\text{ }\Omega$। প্রতিবন্ধকতা $Z = \sqrt{R^2 + X_L^2} = \sqrt{30^2 + 40^2} = \sqrt{900 + 1600} = 50.0\text{ }\Omega$। ক্ষমতা গুণক $\cos\phi = \frac{R}{Z} = \frac{30}{50} = 0.60$। কারেন্ট $I = \frac{V}{Z} = \frac{220}{50} = 4.40\text{ A}$। ব্যয়িত ক্ষমতা $P = V I \cos\phi = 220 \times 4.40 \times 0.60 = 580.8\text{ W}$ (বা $I^2 R = 4.4^2 \times 30 = 19.36 \times 30 = 580.8\text{ W}$)।</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 16</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
+          <t>ক্ষমতা গুণক $\cos\phi = 0.60$, ব্যয়িত ক্ষমতা $P = 580.8\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4494,38 +4230,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান (সমস্যা 17)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>[সমস্যা 17: পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান]
-একটি সাইনুসয়েডাল পরিবর্তী ভোল্টেজের সমীকরণ $V(t) = 1200 \sin(500\pi t)\text{ V}$। উৎসটির শীর্ষ ভোল্টেজ ($V_0$), কার্যকর ভোল্টেজ ($V_{rms}$) এবং কম্পাঙ্ক ($f$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি খাঁটি আবেশক বা খাঁটি ধারকযুক্ত বর্তনীতে তড়িৎ প্রবাহ চললেও ব্যয়িত গড় ক্ষমতা কেন শূন্য হয় এবং ওয়াটহীন প্রবাহ (Wattless current) কী?</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 17)।</t>
+          <t>খাঁটি আবেশকে ভোল্টেজ কারেন্টের চেয়ে $90^\circ$ এগিয়ে থাকে এবং ধারকে $90^\circ$ পিছিয়ে থাকে। উভয় ক্ষেত্রেই $\phi = \pm \pi/2$, ফলে ক্ষমতা গুণক $\cos\phi = \cos(\pm 90^\circ) = 0$। গড় ক্ষমতা $P_{\text{avg}} = V I \cos\phi = 0$। কোনো ক্ষমতা অপচয় না করে বর্তনীতে যে প্রবাহ চলে তাকে ওয়াটহীন কারেন্ট বলে।</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 17</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
+          <t>দশা পার্থক্য $\phi = 90^\circ$ হওয়ায় ক্ষমতা গুণক $\cos 90^\circ = 0$, ফলে $P_{\text{avg}} = 0$</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4545,7 +4281,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত (সমস্যা 18)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -4558,25 +4294,25 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>[সমস্যা 18: আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত]
-একটি $L = 0.2\text{ H}$ আবেশকের মধ্য দিয়ে $f = 50\text{ Hz}$ কম্পাঙ্কের পরিবর্তী প্রবাহ চলছে। আবেশকটির আবেশীয় প্রতিঘাত ($X_L = 2\pi f L$) কত ওহম?</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি চোক কয়েলের (Choke coil) বৈশিষ্ট্য: এসি বর্তনীতে রোধকের পরিবর্তে চোক কয়েল ব্যবহার করে প্রবাহ নিয়ন্ত্রণের সুবিধা কী?</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 18)।</t>
+          <t>সাধারণ রোধকে কারেন্ট কমাতে গেলে $I^2 R$ হারে বিপুল তাপ শক্তি অপচয় হয়। কিন্তু চোক কয়েলে $R \approx 0$ এবং $L$ অনেক বেশি হওয়ায় এর ক্ষমতা গুণক $\cos\phi \approx 0$ থাকে; ফলে কার্যকরভাবে কারেন্ট হ্রাস পেলেও বিদ্যুৎ শক্তির অপচয় নগণ্য হয়।</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 18</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
+          <t>চোক কয়েলের উচ্চ আবেশাঙ্ক $L$ এবং নগণ্য রোধ $R$ থাকায় এটি ক্ষমতা অপচয় ছাড়াই প্রবাহ নিয়ন্ত্রণ করে</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4596,38 +4332,38 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>বর্তনীর ক্ষমতা গুণক (Power Factor) (সমস্যা 19)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HARD</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>[সমস্যা 19: বর্তনীর ক্ষমতা গুণক (Power Factor)]
-একটি পরিবর্তী বর্তনীতে রোধ $R = 40\ \Omega$ এবং মোট প্রতিবন্ধকতা $Z = 90\ \Omega$। বর্তনীর ক্ষমতা গুণক ($\\cos\phi = R/Z$) কত এবং $V_{rms} = 220\text{ V}$ হলে ব্যয়িত গড় ক্ষমতা কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি সাইনোসয়েডাল ভোল্টেজের অর্ধ চক্রের গড় মান $V_{	ext{avg}} = rac{2}{\pi}V_0 pprox 0.637 V_0$ প্রমাণ কর।</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 19)।</t>
+          <t>অর্ধ চক্রে ($0$ হতে $T/2$): $V_{\text{avg}} = \frac{1}{T/2}\int_0^{T/2} V_0\sin(\omega t)dt = \frac{2V_0}{T}\left[-\frac{\cos(\omega t)}{\omega}\right]_0^{T/2} = \frac{2V_0}{\omega T}[-\cos\pi + \cos 0] = \frac{2V_0}{2\pi}[-(-1) + 1] = \frac{V_0}{\pi}(2) = \frac{2}{\pi}V_0 \approx 0.6366 V_0$।</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 19</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+          <t>$V_{\text{avg}} = \frac{2}{\pi}V_0 \approx 0.637 V_0$</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4647,7 +4383,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ (সমস্যা 20)</t>
+          <t>পরিবর্তী প্রবাহ, আরএমএস মান ও ফেজর চিত্র (Alternating Current &amp; Phasors)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4660,25 +4396,25 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>[সমস্যা 20: ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ]
-একটি আয়তাকার কুণ্ডলী $N = 600$ পাক এবং ক্ষেত্রফল $A = 0.01\text{ m}^2$। এটি $B = 0.5\text{ T}$ চৌম্বক ক্ষেত্রে $\omega = 100\pi\text{ rad/s}$ বেগে ঘুরলে সর্বোচ্চ আবিষ্ট ভোল্টেজ ($e_0 = NAB\omega$) কত?</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরিবর্তী ভোল্টেজ $V = 100\sin(100\pi t)$ এবং প্রবাহ $I = 2\sin(100\pi t - \pi/3)$। বর্তনীর ক্ষমতা গুণক এবং ব্যয়িত গড় ক্ষমতা কত?</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 20)।</t>
+          <t>দশা পার্থক্য $\phi = \frac{\pi}{3} = 60^\circ$। ক্ষমতা গুণক $\cos 60^\circ = 0.50$। $V_{\text{rms}} = \frac{100}{\sqrt{2}}$, $I_{\text{rms}} = \frac{2}{\sqrt{2}} = \sqrt{2}$। গড় ক্ষমতা $P = V_{\text{rms}} I_{\text{rms}} \cos\phi = \left(\frac{100}{\sqrt{2}}\right)(\sqrt{2})(0.50) = 50.0\text{ W}$।</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 20</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
+          <t>ক্ষমতা গুণক $\cos\phi = 0.50$, গড় ক্ষমতা $P = 50.0\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4698,44 +4434,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা (সমস্যা 21)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##
-[সমস্যা 21: শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা]
-##PRESET:circuit-ac[size:medium]##
-একটি শ্রেণি RLC বর্তনীতে $R = 80\ \Omega$, $L = 0.3\text{ H}$ এবং $C = 10\ \mu\text{F}$ যুক্ত করে $V = 220\text{ V}$ পরিবর্তী উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর অনুনাদী কম্পাঙ্ক ($f_0$) এবং অনুনাদ অবস্থায় শীর্ষ প্রবাহ নির্ণয় কর।</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি শ্রেণি $LCR$ বর্তনীতে $R = 10.0\text{ }\Omega$, $L = 0.10\text{ H}$ এবং $C = 10.0\text{ }\mu	ext{F}$। বর্তনীটির অনুনাদী কম্পাঙ্ক (Resonant frequency $f_0$) এবং অনুনাদের মুহূর্তে এর কোয়ালিটি ফ্যাক্টর ($Q$-factor) নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 21)।</t>
+          <t>অনুনাদী কম্পাঙ্ক $f_0 = \frac{1}{2\pi\sqrt{LC}} = \frac{1}{2\pi\sqrt{0.10 \times 10 \times 10^{-6}}} = \frac{1}{2\pi\sqrt{10^{-6}}} = \frac{1}{2\pi \times 10^{-3}} = \frac{1000}{2\pi} \approx 159.155\text{ Hz}$। কোয়ালিটি ফ্যাক্টর $Q = \frac{1}{R}\sqrt{\frac{L}{C}} = \frac{1}{10}\sqrt{\frac{0.10}{10 \times 10^{-6}}} = \frac{1}{10}\sqrt{10000} = \frac{100}{10} = 10.0$।</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 21</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
+          <t>অনুনাদী কম্পাঙ্ক $f_0 = 159.15\text{ Hz}$, কোয়ালিটি ফ্যাক্টর $Q = 10.0$</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4755,12 +4485,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ (সমস্যা 22)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -4768,31 +4498,25 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##
-[সমস্যা 22: স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ]
-##PRESET:transformer[size:medium]##
-একটি আদর্শ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 1000$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 50$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করলে গৌণ কুণ্ডলীর প্রান্তীয় ভোল্টেজ এবং মুখ্য প্রবাহ $1\text{ A}$ হলে গৌণ প্রবাহ কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি শ্রেণি $LCR$ বর্তনীতে $R = 20\text{ }\Omega, X_L = 80\text{ }\Omega$ এবং $X_C = 65\text{ }\Omega$। বর্তনীটিকে $250\text{ V}$ উৎসে যুক্ত করলে মোট প্রতিবন্ধকতা $Z$, প্রবাহ $I$, এবং প্রতিটি উপাদানের দুই প্রান্তের বিভব পার্থক্য $V_R, V_L, V_C$ নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 22)।</t>
+          <t>নিট ঘাত $X = X_L - X_C = 80 - 65 = 15.0\text{ }\Omega$। প্রতিবন্ধকতা $Z = \sqrt{R^2 + X^2} = \sqrt{20^2 + 15^2} = \sqrt{400 + 225} = \sqrt{625} = 25.0\text{ }\Omega$। প্রবাহ $I = \frac{V}{Z} = \frac{250}{25} = 10.0\text{ A}$। উপাদানের বিভব: $V_R = I R = 10 \times 20 = 200.0\text{ V}$। $V_L = I X_L = 10 \times 80 = 800.0\text{ V}$। $V_C = I X_C = 10 \times 65 = 650.0\text{ V}$। লক্ষণীয় যে ফেজর যোগফল $\sqrt{V_R^2 + (V_L - V_C)^2} = \sqrt{200^2 + 150^2} = 250\text{ V} = V_{\text{source}}$।</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 22</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
+          <t>$Z = 25.0\text{ }\Omega, I = 10.0\text{ A}, V_R = 200.0\text{ V}, V_L = 800.0\text{ V}, V_C = 650.0\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4812,38 +4536,38 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল (সমস্যা 23)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>[সমস্যা 23: ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল]
-একটি $N = 1200$ পাকের কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স $\Delta t = 0.7\text{ s}$-এ $0.08\text{ Wb}$ হতে $0.02\text{ Wb}$-এ হ্রাস পেল। কুণ্ডলীতে আবিষ্ট গড় তড়িচ্চালক বল ($e = -N\frac{\Delta\Phi}{\Delta t}$) কত ভোল্ট?</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি আদর্শ স্টেপ-আপ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 100$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 2000$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করা হলে গৌণ কুণ্ডলীর ভোল্টেজ কত? গৌণে $4400\text{ }\Omega$ লোড রোধ যুক্ত করলে মুখ্য কুণ্ডলীর প্রবাহ কত?</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 23)।</t>
+          <t>রূপান্তর অনুপাত $\frac{V_s}{V_p} = \frac{N_s}{N_p} \implies V_s = 220 \times \frac{2000}{100} = 220 \times 20 = 4400.0\text{ V}$। গৌণ প্রবাহ $I_s = \frac{V_s}{R_L} = \frac{4400}{4400} = 1.0\text{ A}$। আদর্শ ট্রান্সফরমারে ইনপুট ক্ষমতা = আউটপুট ক্ষমতা: $V_p I_p = V_s I_s \implies I_p = I_s\left(\frac{V_s}{V_p}\right) = 1.0 \times 20 = 20.0\text{ A}$।</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 23</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
+          <t>গৌণ ভোল্টেজ $V_s = 4400.0\text{ V}$, মুখ্য কুণ্ডলীর কারেন্ট $I_p = 20.0\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4863,12 +4587,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ (সমস্যা 24)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -4876,25 +4600,25 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>[সমস্যা 24: ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ]
-$L = 1.0\text{ m}$ দীর্ঘ একটি ধাতব পরিবাহী দণ্ড $B = 0.2\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে এক প্রান্তকে কেন্দ্র করে $\omega = 90\text{ rad/s}$ কৌণিক দ্রুতিতে ঘুরছে। দণ্ডের দুই প্রান্তের মধ্যে আবিষ্ট বিভব পার্থক্য ($e = \frac{1}{2}B\omega L^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি ট্রান্সফরমারের কর্মদক্ষতা $\eta = 90\%$। এটি $220\text{ V}$ লাইনে কাজ করে $11\text{ V}, 8.0\text{ A}$-এর একটি বাতিতে বিদ্যুৎ সরবরাহ করে। ট্রান্সফরমারটির মুখ্য কুণ্ডলীর তড়িৎ প্রবাহ কত?</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 24)।</t>
+          <t>আউটপুট ক্ষমতা $P_{\text{out}} = V_s I_s = 11\text{ V} \times 8.0\text{ A} = 88.0\text{ W}$। দক্ষতা $\eta = \frac{P_{\text{out}}}{P_{\text{in}}} \implies P_{\text{in}} = \frac{88.0}{0.90} \approx 97.78\text{ W}$। আবার $P_{\text{in}} = V_p I_p \implies I_p = \frac{P_{\text{in}}}{V_p} = \frac{97.78}{220} \approx 0.4444\text{ A}$।</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 24</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+          <t>মুখ্য কুণ্ডলীর প্রবাহ $I_p = 0.444\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4914,38 +4638,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি (সমস্যা 25)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>[সমস্যা 25: স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি]
-একটি কুণ্ডলীর স্বকীয় আবেশাঙ্ক $L = 4.0\text{ H}$। এর মধ্য দিয়ে বিদ্যুৎ প্রবাহ $0.1\text{ s}$ সময়ে $1\text{ A}$ হতে শূন্যে নেমে এলে আবিষ্ট ইএমএফ এবং প্রাথমিক অবস্থায় সঞ্চিত শক্তি ($U = \frac{1}{2}LI^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি অনুনাদী বর্তনীতে $L = 1.0\text{ mH}$ এবং ধারকত্ব পরিবর্তনশীল। বর্তনীটিকে $500\text{ kHz}$ হতে $1500\text{ kHz}$ মধ্যম তরঙ্গ (Medium wave AM radio band) টিউন করতে ধারকের ধারকত্ব পরিসর ($C_{\min}$ হতে $C_{\max}$) কত হতে হবে?</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 25)।</t>
+          <t>$f = \frac{1}{2\pi\sqrt{LC}} \implies C = \frac{1}{4\pi^2 f^2 L}$। সর্বোচ্চ কম্পাঙ্কে ($f_{\max} = 1.5 \times 10^6\text{ Hz}$): $C_{\min} = \frac{1}{4\pi^2 (1.5 \times 10^6)^2 (10^{-3})} = \frac{1}{4\pi^2 (2.25 \times 10^{12}) \times 10^{-3}} = \frac{1}{8.8826 \times 10^{10}} \approx 1.126 \times 10^{-11}\text{ F} = 11.26\text{ pF}$। সর্বনিম্ন কম্পাঙ্কে ($f_{\min} = 5.0 \times 10^5\text{ Hz}$): $C_{\max} = C_{\min} \times (1500/500)^2 = 11.26 \times 9 \approx 101.32\text{ pF}$।</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 25</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
+          <t>ধারকত্ব পরিসর $C = 11.26\text{ pF}$ হতে $101.32\text{ pF}$</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4965,12 +4689,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ (সমস্যা 26)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -4978,25 +4702,25 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>[সমস্যা 26: পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ]
-দুটি পাশাপাশি রাখা কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক $M = 0.6\text{ H}$। মুখ্য কুণ্ডলীতে প্রবাহ $\Delta t = 0.05\text{ s}$-এ শূন্য হতে $3\text{ A}$-তে উন্নীত করলে গৌণ কুণ্ডলীতে আবিষ্ট ইএমএফ কত?</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $LCR$ শ্রেণি বর্তনীতে অনুনাদের শর্ত প্রমাণ কর এবং দেখাও যে অনুনাদের সময় বর্তনীর প্রতিবন্ধকতা ন্যূনতম ($Z = R$), প্রবাহ সর্বোচ্চ ($I_{\max} = V/R$) এবং ক্ষমতা গুণক একক ($\cos\phi = 1$) হয়।</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 26)।</t>
+          <t>প্রতিবন্ধকতা $Z = \sqrt{R^2 + (X_L - X_C)^2}$। $Z$-কে ন্যূনতম করতে $(X_L - X_C)^2 = 0 \implies X_L = X_C \implies \omega L = \frac{1}{\omega C} \implies \omega_0 = \frac{1}{\sqrt{LC}}$। এই অবস্থায় $Z = \sqrt{R^2 + 0} = R$ (ন্যূনতম)। প্রবাহ $I = V/R$ (সর্বোচ্চ)। দশা কোণ $\tan\phi = 0 \implies \phi = 0 \implies \cos\phi = 1$।</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 26</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
+          <t>শর্ত $X_L = X_C \implies \omega_0 = \frac{1}{\sqrt{LC}}$, $Z_{\min} = R, \cos\phi = 1.0$</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5016,38 +4740,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান (সমস্যা 27)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>[সমস্যা 27: পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান]
-একটি সাইনুসয়েডাল পরিবর্তী ভোল্টেজের সমীকরণ $V(t) = 800 \sin(500\pi t)\text{ V}$। উৎসটির শীর্ষ ভোল্টেজ ($V_0$), কার্যকর ভোল্টেজ ($V_{rms}$) এবং কম্পাঙ্ক ($f$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ট্রান্সফরমারের মুখ্য কুণ্ডলীতে পাকসংখ্যা $400$ এবং গৌণ কুণ্ডলীতে পাকসংখ্যা $2000$। ট্রান্সফরমারটি কি স্টেপ-আপ না স্টেপ-ডাউন? যদি ইনপুট ডিসি $12\text{ V}$ ব্যাটারি সংযোগ দেওয়া হয়, তবে আউটপুট ভোল্টেজ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 27)।</t>
+          <t>পাকসংখ্যা $N_s &gt; N_p$ হওয়ায় এটি স্টেপ-আপ ট্রান্সফরমার। কিন্তু ট্রান্সফরমার কেবল সময়ের সাথে পরিবর্তনশীল ফ্লাক্সের ভিত্তিতে ফ্যারাডের আবেশ নীতিতে কাজ করে ($\mathcal{E} = -N d\Phi/dt$)। স্থির ডিসি সংযোগ দিলে ফ্লাক্স ধ্রুব থাকে ($d\Phi/dt = 0$), ফলে গৌণ কুণ্ডলীতে কোনো ভোল্টেজ আবিষ্ট হয় না ($V_s = 0$) এবং দীর্ঘক্ষণ ডিসি সংযোগ রাখলে মুখ্য কুণ্ডলী পুড়ে যেতে পারে।</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 27</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
+          <t>ট্রান্সফরমারটি স্টেপ-আপ, কিন্তু ডিসি ইনপুটে আউটপুট ভোল্টেজ শূন্য ($0\text{ V}$) হবে</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5067,12 +4791,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত (সমস্যা 28)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F79" t="n">
@@ -5080,25 +4804,25 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>[সমস্যা 28: আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত]
-একটি $L = 0.10\text{ H}$ আবেশকের মধ্য দিয়ে $f = 50\text{ Hz}$ কম্পাঙ্কের পরিবর্তী প্রবাহ চলছে। আবেশকটির আবেশীয় প্রতিঘাত ($X_L = 2\pi f L$) কত ওহম?</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $LC$ স্পন্দনশীল বর্তনীতে (LC Oscillations) মোট শক্তির সংরক্ষণশীলতা প্রমাণ কর। দেখাও যে আধানের সমীকরণ $q(t) = Q_0\cos(\omega t)$ এবং শক্তির মোট মান $rac{Q_0^2}{2C}$ স্থির থাকে।</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 28)।</t>
+          <t>ধারকের তড়িৎ শক্তি $U_E = \frac{q^2}{2C} = \frac{Q_0^2\cos^2(\omega t)}{2C}$। প্রবাহ $I = -\frac{dq}{dt} = \omega Q_0\sin(\omega t)$। আবেশকের চৌম্বক শক্তি $U_B = \frac{1}{2}L I^2 = \frac{1}{2}L \omega^2 Q_0^2\sin^2(\omega t) = \frac{Q_0^2\sin^2(\omega t)}{2C}$ (যেহেতু $\omega^2 = \frac{1}{LC}$)। মোট শক্তি $E = U_E + U_B = \frac{Q_0^2}{2C}(\cos^2\omega t + \sin^2\omega t) = \frac{Q_0^2}{2C}$ যা সময় নিরপেক্ষ ও সংরক্ষিত।</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 28</t>
-        </is>
-      </c>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
+          <t>মোট শক্তি $E = U_E + U_B = \frac{q^2}{2C} + \frac{1}{2}L I^2 = \frac{Q_0^2}{2C} = \text{ধ্রুবক}$</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5118,38 +4842,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>বর্তনীর ক্ষমতা গুণক (Power Factor) (সমস্যা 29)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>[সমস্যা 29: বর্তনীর ক্ষমতা গুণক (Power Factor)]
-একটি পরিবর্তী বর্তনীতে রোধ $R = 120\ \Omega$ এবং মোট প্রতিবন্ধকতা $Z = 90\ \Omega$। বর্তনীর ক্ষমতা গুণক ($\\cos\phi = R/Z$) কত এবং $V_{rms} = 220\text{ V}$ হলে ব্যয়িত গড় ক্ষমতা কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি পরিবর্তী ভোল্টেজ $V = 200\sqrt{2}\sin(100 t)$ একটি $LCR$ বর্তনীতে প্রযুক্ত যার $R = 10\text{ }\Omega, L = 50\text{ mH}, C = 200\text{ }\mu	ext{F}$। বর্তনীতে ভোল্টেজ ও প্রবাহের শীর্ষ মান নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 29)।</t>
+          <t>$\omega = 100\text{ rad/s}$। $X_L = \omega L = 100 \times 0.050 = 5.0\text{ }\Omega$। $X_C = \frac{1}{\omega C} = \frac{1}{100 \times 200 \times 10^{-6}} = \frac{1}{0.02} = 50.0\text{ }\Omega$। নিট ঘাত $X = X_C - X_L = 50 - 5 = 45.0\text{ }\Omega$। প্রতিবন্ধকতা $Z = \sqrt{10^2 + 45^2} = \sqrt{100 + 2025} = \sqrt{2125} \approx 46.10\text{ }\Omega$। শীর্ষ কারেন্ট $I_0 = \frac{V_0}{Z} = \frac{200\sqrt{2}}{46.10} \approx \frac{282.84}{46.10} \approx 6.135\text{ A}$।</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 29</t>
-        </is>
-      </c>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+          <t>ভোল্টেজ শীর্ষ $V_0 = 282.8\text{ V}$, প্রবাহ শীর্ষ $I_0 = 5.54\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5169,12 +4893,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ (সমস্যা 30)</t>
+          <t>এলসিআর অনুনাদ ও ট্রান্সফরমার (LCR Resonance &amp; Transformers)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F81" t="n">
@@ -5182,25 +4906,25 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>[সমস্যা 30: ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ]
-একটি আয়তাকার কুণ্ডলী $N = 200$ পাক এবং ক্ষেত্রফল $A = 0.01\text{ m}^2$। এটি $B = 0.5\text{ T}$ চৌম্বক ক্ষেত্রে $\omega = 100\pi\text{ rad/s}$ বেগে ঘুরলে সর্বোচ্চ আবিষ্ট ভোল্টেজ ($e_0 = NAB\omega$) কত?</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr"/>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##
+একটি দূরপাল্লার বিদ্যুৎ সঞ্চালন লাইনে $20\text{ km}$ দূরত্বে $110\text{ kW}$ বিদ্যুৎ পাঠাতে হবে। লাইনের প্রতি কিমির রোধ $0.5\text{ }\Omega$। (ক) $220\text{ V}$-এ এবং (খ) $22000\text{ V}$-এ প্রেরণে লাইনের ভোল্টেজ পতন এবং অপচয় ক্ষমতার তুলনা কর।</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=5,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 30)।</t>
+          <t>লাইনের মোট রোধ $R = 20 \times 0.5 = 10.0\text{ }\Omega$। (ক) $220\text{ V}$-এ কারেন্ট $I_1 = \frac{110000}{220} = 500\text{ A}$। লাইনে ভোল্টেজ পতন $= 500 \times 10 = 5000\text{ V} &gt; 220\text{ V}$ (সম্পূর্ণ অসম্ভব)। (খ) $22000\text{ V}$-এ কারেন্ট $I_2 = \frac{110000}{22000} = 5.0\text{ A}$। লাইনে পতন $= 5.0 \times 10 = 50\text{ V}$। লাইনে অপচয় $P_{\text{loss}} = I_2^2 R = 5^2 \times 10 = 250.0\text{ W}$ (উৎপন্ন ক্ষমতার মাত্র $0.23\%$ অপচয়)।</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 30</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
+          <t>(ক) $220\\text{ V}$-এ প্রেরণ অবাস্তব (অপচয় $2.5\\text{ MW}$), (খ) $22000\\text{ V}$-এ লাইনে অপচয় মাত্র $250.0\\text{ W}$</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5220,44 +4944,38 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা (সমস্যা 31)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##
-[সমস্যা 31: শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা]
-##PRESET:circuit-ac[size:medium]##
-একটি শ্রেণি RLC বর্তনীতে $R = 40\ \Omega$, $L = 0.3\text{ H}$ এবং $C = 10\ \mu\text{F}$ যুক্ত করে $V = 220\text{ V}$ পরিবর্তী উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর অনুনাদী কম্পাঙ্ক ($f_0$) এবং অনুনাদ অবস্থায় শীর্ষ প্রবাহ নির্ণয় কর।</t>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $LCR$ বর্তনীতে অনুনাদের সময় অর্ধ-ক্ষমতা কম্পাঙ্কদ্বয় (Half-power frequencies) যথাক্রমে $f_1 = 95\text{ kHz}$ এবং $f_2 = 105\text{ kHz}$। বর্তনীটির ব্যান্ডউইডথ (Bandwidth $\Delta f$), অনুনাদী কম্পাঙ্ক $f_0$ এবং $Q$-ফ্যাক্টর নির্ণয় কর।</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##</t>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 31)।</t>
+          <t>ব্যান্ডউইডথ $\Delta f = f_2 - f_1 = 105 - 95 = 10.0\text{ kHz}$। অনুনাদী কম্পাঙ্ক $f_0 = \frac{f_1 + f_2}{2} = \frac{95 + 105}{2} = 100.0\text{ kHz}$। অনুনাদের তীক্ষ্ণতা বা $Q$-ফ্যাক্টর: $Q = \frac{f_0}{\Delta f} = \frac{100}{10} = 10.0$।</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 31</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
+          <t>ব্যান্ডউইডথ $\Delta f = 10.0\text{ kHz}$, অনুনাদী কম্পাঙ্ক $f_0 = 100.0\text{ kHz}$, $Q = 10.0$</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5277,12 +4995,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ (সমস্যা 32)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F83" t="n">
@@ -5290,31 +5008,25 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##
-[সমস্যা 32: স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ]
-##PRESET:transformer[size:medium]##
-একটি আদর্শ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 600$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 50$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করলে গৌণ কুণ্ডলীর প্রান্তীয় ভোল্টেজ এবং মুখ্য প্রবাহ $1\text{ A}$ হলে গৌণ প্রবাহ কত?</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি সমান্তরাল $L-C$ বর্তনীতে (Rejector circuit) আবেশক $L$ এবং ধারক $C$ সমান্তরালে যুক্ত। আদর্শ ক্ষেত্রে (রোধ শূন্য) এই বর্তনীর অনুনাদী কম্পাঙ্কে মোট প্রতিবন্ধকতা কত হয়?</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 32)।</t>
+          <t>সমান্তরাল সমবায়ে প্রবেশ্যতা (Admittance) $Y = \frac{1}{j\omega L} + j\omega C = j\left(\omega C - \frac{1}{\omega L}\right)$। অনুনাদী শর্তে $\omega_0 C = \frac{1}{\omega_0 L} \implies Y = 0$। ফলে প্রতিবন্ধকতা $Z = \frac{1}{Y} \to \infty$ (অসীম রোধ সৃষ্টি করে, ফলে নির্দিষ্ট কম্পাঙ্কের সংকেত সম্পূর্ণ আটকে দেয়—তাই একে রিজেক্টর সার্কিট বলে)।</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 32</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
+          <t>প্রতিবন্ধকতা অসীম ($Z \to \infty$)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5334,38 +5046,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল (সমস্যা 33)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>[সমস্যা 33: ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল]
-একটি $N = 800$ পাকের কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স $\Delta t = 0.7\text{ s}$-এ $0.08\text{ Wb}$ হতে $0.02\text{ Wb}$-এ হ্রাস পেল। কুণ্ডলীতে আবিষ্ট গড় তড়িচ্চালক বল ($e = -N\frac{\Delta\Phi}{\Delta t}$) কত ভোল্ট?</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $200\text{ V}, 50\text{ Hz}$ লাইনে যুক্ত একটি মোটরের ক্ষমতা $P = 1.0\text{ kW}$ এবং এর ক্ষমতা গুণক $\cos\phi = 0.5$ ল্যাগিং। ক্ষমতা গুণককে বাড়িয়ে $0.90$-এ উন্নীত করতে মোটরের সাথে কত ধারকত্বের ধারক সমান্তরালে যুক্ত করতে হবে?</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 33)।</t>
+          <t>আদি কারেন্ট $I_1 = \frac{P}{V\cos\phi_1} = \frac{1000}{200 \times 0.5} = 10\text{ A}$। $\tan\phi_1 = \tan(60^\circ) = \sqrt{3} \approx 1.732$। নতুন $\cos\phi_2 = 0.90 \implies \phi_2 \approx 25.84^\circ \implies \tan\phi_2 \approx 0.484$। প্রয়োজনীয় রিঅ্যাক্টিভ পাওয়ার ক্ষতিপূরণ: $Q_c = P(\tan\phi_1 - \tan\phi_2) = 1000(1.732 - 0.484) = 1248\text{ VAR}$। ধারকত্ব $C = \frac{Q_c}{\omega V^2} = \frac{1248}{2\pi(50)(200)^2} = \frac{1248}{314.16 \times 40000} = \frac{1248}{1.2566 \times 10^7} \approx 9.93 \times 10^{-5}\text{ F} \approx 99.3\text{ }\mu\text{F}$।</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 33</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
+          <t>প্রয়োজনীয় ধারকত্ব $C = 99.2\text{ }\mu\text{F}$</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5385,12 +5097,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ (সমস্যা 34)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -5398,25 +5110,25 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>[সমস্যা 34: ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ]
-$L = 1.0\text{ m}$ দীর্ঘ একটি ধাতব পরিবাহী দণ্ড $B = 0.10\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে এক প্রান্তকে কেন্দ্র করে $\omega = 90\text{ rad/s}$ কৌণিক দ্রুতিতে ঘুরছে। দণ্ডের দুই প্রান্তের মধ্যে আবিষ্ট বিভব পার্থক্য ($e = \frac{1}{2}B\omega L^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি তারের কুণ্ডলীকে ডিসি উৎসে যুক্ত করলে $10\text{ V}$ বিভবে $2.0\text{ A}$ কারেন্ট চলে। কিন্তু একে $10\text{ V}, 50\text{ Hz}$ এসি উৎসে যুক্ত করলে প্রবাহ কমে $1.0\text{ A}$ হয়। কুণ্ডলীর রোধ $R$ এবং স্ববেশাঙ্ক $L$ নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 34)।</t>
+          <t>ডিসি ক্ষেত্রে কেবল ওহমিক রোধ বাধা দেয়: $R = \frac{V_{\text{dc}}}{I_{\text{dc}}} = \frac{10}{2.0} = 5.0\text{ }\Omega$। এসি ক্ষেত্রে প্রতিবন্ধকতা $Z = \frac{V_{\text{ac}}}{I_{\text{ac}}} = \frac{10}{1.0} = 10.0\text{ }\Omega$। আবেশীয় ঘাত $X_L = \sqrt{Z^2 - R^2} = \sqrt{10^2 - 5^2} = \sqrt{100 - 25} = \sqrt{75} \approx 8.66\text{ }\Omega$। স্ববেশাঙ্ক $L = \frac{X_L}{2\pi f} = \frac{8.66}{2\pi \times 50} = \frac{8.66}{314.16} \approx 0.02757\text{ H} \approx 27.6\text{ mH}$।</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 34</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
+          <t>রোধ $R = 5.0\text{ }\Omega$, স্ববেশাঙ্ক $L = 27.6\text{ mH}$</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5436,38 +5148,38 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি (সমস্যা 35)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>[সমস্যা 35: স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি]
-একটি কুণ্ডলীর স্বকীয় আবেশাঙ্ক $L = 12.0\text{ H}$। এর মধ্য দিয়ে বিদ্যুৎ প্রবাহ $0.1\text{ s}$ সময়ে $1\text{ A}$ হতে শূন্যে নেমে এলে আবিষ্ট ইএমএফ এবং প্রাথমিক অবস্থায় সঞ্চিত শক্তি ($U = \frac{1}{2}LI^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>##GEO:rect[w=3,h=3][size:small]##
+একটি বর্গাকার কুণ্ডলীর প্রতি বাহুর দৈর্ঘ্য $10\text{ cm}$ এবং রোধ $0.5\text{ }\Omega$। কুণ্ডলীটি একটি সুষম চৌম্বক ক্ষেত্র $B = 1.0\text{ T}$-এ তার তলে লম্বভাবে অবস্থিত। কুণ্ডলীটিকে $0.1\text{ সেকেন্ডে}$ $180^\circ$ কোণে উল্টে দেওয়া হলে কুণ্ডলীতে গড় আবিষ্ট তড়িচ্চালক বল এবং প্রবাহিত মোট আধান কত?</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=3,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 35)।</t>
+          <t>আদি ফ্লাক্স $\Phi_1 = B A = 1.0 \times (0.10)^2 = 0.010\text{ Wb}$। $180^\circ$ উল্টালে অন্তিম ফ্লাক্স $\Phi_2 = -B A = -0.010\text{ Wb}$। ফ্লাক্স পরিবর্তন $\Delta\Phi = \Phi_1 - \Phi_2 = 2BA = 0.020\text{ Wb}$। গড় $\text{EMF} \mathcal{E} = \frac{\Delta\Phi}{\Delta t} = \frac{0.020}{0.10} = 0.20\text{ V}$। প্রবাহিত আধান $Q = \frac{\Delta\Phi}{R} = \frac{0.020\text{ Wb}}{0.5\text{ }\Omega} = 0.040\text{ C}$।</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 35</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>আবিষ্ট $\text{EMF} \mathcal{E} = 0.20\text{ V}$, প্রবাহিত আধান $Q = 0.040\text{ C}$</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5487,12 +5199,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ (সমস্যা 36)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -5500,25 +5212,25 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>[সমস্যা 36: পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ]
-দুটি পাশাপাশি রাখা কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক $M = 0.2\text{ H}$। মুখ্য কুণ্ডলীতে প্রবাহ $\Delta t = 0.05\text{ s}$-এ শূন্য হতে $3\text{ A}$-তে উন্নীত করলে গৌণ কুণ্ডলীতে আবিষ্ট ইএমএফ কত?</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি আরএল ($RL$) ডিসি বর্তনীতে সংযোগ দেওয়ার পর কারেন্ট বৃদ্ধির সমীকরণ $I(t) = rac{E}{R}(1 - e^{-t/	au})$। সময় ধ্রুবক $	au = L/R$-এর ভৌত তাৎপর্য কী এবং $	au$ সময়ে কারেন্ট সর্বোচ্চ মানের শতকরা কত অংশ হয়?</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 36)।</t>
+          <t>$t = \tau = L/R$ বসালে: $I(\tau) = I_0 (1 - e^{-1}) = I_0(1 - 0.3679) = 0.6321 I_0$। অর্থাৎ সময় ধ্রুবক হলো সেই সময় যাতে কারেন্ট শূন্য হতে তার সর্বোচ্চ স্থির মানের প্রায় $63.2\%$ মানে পৌঁছায়।</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 36</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
+          <t>$\tau$ সময়ে কারেন্ট সর্বোচ্চ মানের $63.2\%$ বৃদ্ধি পায়</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5538,38 +5250,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান (সমস্যা 37)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>[সমস্যা 37: পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান]
-একটি সাইনুসয়েডাল পরিবর্তী ভোল্টেজের সমীকরণ $V(t) = 400 \sin(500\pi t)\text{ V}$। উৎসটির শীর্ষ ভোল্টেজ ($V_0$), কার্যকর ভোল্টেজ ($V_{rms}$) এবং কম্পাঙ্ক ($f$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি $10\text{ H}$ আবেশক এবং $100\text{ }\Omega$ রোধক বিশিষ্ট কয়েলকে $20\text{ V}$ ব্যাটারির সাথে যুক্ত করা হলো। বর্তনীটির সময় ধ্রুবক $	au$ কত এবং সংযোগ বিচ্ছিন্ন করার কত সময় পর কারেন্ট তার আদি মানের $10\%$ এ নেমে আসবে?</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 37)।</t>
+          <t>সময় ধ্রুবক $\tau = \frac{L}{R} = \frac{10}{100} = 0.10\text{ s}$। কারেন্ট হ্রাসের সমীকরণ: $I(t) = I_0 e^{-t/\tau} = 0.10 I_0 \implies e^{-t/\tau} = 0.10 \implies e^{t/\tau} = 10 \implies t = \tau \ln(10) = 0.10 \times 2.3026 \approx 0.230\text{ s}$।</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 37</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
+          <t>সময় ধ্রুবক $\tau = 0.10\text{ s}$, সময় $t = 0.230\text{ s}$</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5589,12 +5301,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত (সমস্যা 38)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -5602,25 +5314,25 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>[সমস্যা 38: আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত]
-একটি $L = 0.6\text{ H}$ আবেশকের মধ্য দিয়ে $f = 50\text{ Hz}$ কম্পাঙ্কের পরিবর্তী প্রবাহ চলছে। আবেশকটির আবেশীয় প্রতিঘাত ($X_L = 2\pi f L$) কত ওহম?</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি পরিবর্তী উৎসের ভোল্টেজ $V = 100\sin(100\pi t)$ এবং প্রবাহ $I = 4\sin(100\pi t + \pi/6)$। বর্তনীটির প্রতিক্রিয়াশীল ক্ষমতা (Reactive power in VAR) এবং দৃশ্যমান ক্ষমতা (Apparent power in VA) নির্ণয় কর।</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 38)।</t>
+          <t>$V_{\text{rms}} = \frac{100}{\sqrt{2}}$, $I_{\text{rms}} = \frac{4}{\sqrt{2}}$। দৃশ্যমান ক্ষমতা $S = V_{\text{rms}} I_{\text{rms}} = \frac{100 \times 4}{2} = 200.0\text{ VA}$। দশা কোণ $\phi = \pi/6 = 30^\circ$। প্রতিক্রিয়াশীল ক্ষমতা $Q = S\sin\phi = 200 \times \sin 30^\circ = 200 \times 0.5 = 100.0\text{ VAR}$। প্রকৃত ক্ষমতা $P = S\cos 30^\circ = 200 \times 0.866 = 173.2\text{ W}$।</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 38</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
+          <t>দৃশ্যমান ক্ষমতা $S = 200.0\text{ VA}$, প্রতিক্রিয়াশীল ক্ষমতা $Q = 100.0\text{ VAR}$</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5640,38 +5352,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>বর্তনীর ক্ষমতা গুণক (Power Factor) (সমস্যা 39)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>[সমস্যা 39: বর্তনীর ক্ষমতা গুণক (Power Factor)]
-একটি পরিবর্তী বর্তনীতে রোধ $R = 80\ \Omega$ এবং মোট প্রতিবন্ধকতা $Z = 90\ \Omega$। বর্তনীর ক্ষমতা গুণক ($\\cos\phi = R/Z$) কত এবং $V_{rms} = 220\text{ V}$ হলে ব্যয়িত গড় ক্ষমতা কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতব বলয়কে একটি উল্লম্ব দণ্ড চুম্বকের ওপর মুক্তভাবে ফেলে দিলে বলয়টির নিম্নমুখী ত্বরণ অভিকর্ষজ ত্বরণ $g$-এর চেয়ে কম, সমান নাকি বেশি হবে এবং কেন?</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 39)।</t>
+          <t>বলয়টি চুম্বকের দিকে পড়ার সময় বলয়ের মধ্য দিয়ে নিম্নমুখী ফ্লাক্স বৃদ্ধি পায়। লেনজের সূত্রানুসারে বলয়ে এমন অভিমুখে কারেন্ট আবিষ্ট হয় যাতে এটি নিচের চুম্বক মেরুকে বিকর্ষণ করে। এই ঊর্ধ্বমুখী চৌম্বক প্রতিরোধক বল ওজনের বিপরীতে কাজ করায় কার্যকর নিম্নমুখী ত্বরণ অভিকর্ষজ ত্বরণের চেয়ে কম হয় ($a &lt; g$)।</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 39</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>ত্বরণ $a &lt; g$ হবে (লেনজের সূত্রে বিপরীতমুখী চৌম্বক বাধার কারণে)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5691,12 +5403,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ (সমস্যা 40)</t>
+          <t>উন্নত এলসিআর নেটওয়ার্ক ও ক্ষণস্থায়ী অবস্থা (Advanced LCR &amp; Transients)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -5704,25 +5416,25 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>[সমস্যা 40: ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ]
-একটি আয়তাকার কুণ্ডলী $N = 1000$ পাক এবং ক্ষেত্রফল $A = 0.01\text{ m}^2$। এটি $B = 0.5\text{ T}$ চৌম্বক ক্ষেত্রে $\omega = 100\pi\text{ rad/s}$ বেগে ঘুরলে সর্বোচ্চ আবিষ্ট ভোল্টেজ ($e_0 = NAB\omega$) কত?</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+দুটি কুণ্ডলীর স্ববেশাঙ্ক যথাক্রমে $L_1 = 4.0\text{ mH}$ এবং $L_2 = 9.0\text{ mH}$। কুণ্ডলীদ্বয়ের মধ্যে নিখুঁত কাপলিং ($k = 1.0$) থাকলে এদের পারস্পরিক আবেশাঙ্ক $M$ কত হবে?</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 40)।</t>
+          <t>পারস্পরিক আবেশের সর্বোচ্চ সম্ভাব্য মান $M = k\sqrt{L_1 L_2}$। নিখুঁত কাপলিংয়ে $k = 1.0 \implies M = \sqrt{4.0 \times 9.0} = \sqrt{36.0} = 6.0\text{ mH}$।</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 40</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
+          <t>পারস্পরিক আবেশাঙ্ক $M = 6.0\text{ mH}$</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5742,44 +5454,38 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা (সমস্যা 41)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##
-[সমস্যা 41: শ্রেণি RLC বর্তনীর অনুনাদ ও প্রতিবন্ধকতা]
-##PRESET:circuit-ac[size:medium]##
-একটি শ্রেণি RLC বর্তনীতে $R = 120\ \Omega$, $L = 0.3\text{ H}$ এবং $C = 10\ \mu\text{F}$ যুক্ত করে $V = 220\text{ V}$ পরিবর্তী উৎসের সাথে সংযোগ দেওয়া হলো। বর্তনীর অনুনাদী কম্পাঙ্ক ($f_0$) এবং অনুনাদ অবস্থায় শীর্ষ প্রবাহ নির্ণয় কর।</t>
+          <t>##GEO:circle[r=3][size:small]##
+একটি সাইক্লোট্রনের ডি-দ্বয়ের ব্যাসার্ধ $R = 0.50\text{ m}$ এবং চৌম্বক ক্ষেত্র $B = 1.5\text{ T}$। একটি ডিউটেরন ($q = 1.6 	imes 10^{-19}\text{ C}, m = 3.34 	imes 10^{-27}\text{ kg}$) সাইক্লোট্রন হতে নির্গমনের মুহূর্তে এর সর্বোচ্চ গতিশক্তি কত $\text{MeV}$ হবে?</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>##PRESET:circuit-ac[size:medium]##</t>
+          <t>##GEO:circle[r=3][size:small]##</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 41)।</t>
+          <t>সর্বোচ্চ বেগ $v_{\max} = \frac{q B R}{m} = \frac{(1.6 \times 10^{-19}) \times 1.5 \times 0.50}{3.34 \times 10^{-27}} = \frac{1.2 \times 10^{-19}}{3.34 \times 10^{-27}} \approx 3.593 \times 10^7\text{ m/s}$। গতিশক্তি $E_k = \frac{1}{2}m v_{\max}^2 = \frac{q^2 B^2 R^2}{2m} = \frac{(1.2 \times 10^{-19})^2}{2(3.34 \times 10^{-27})} = \frac{1.44 \times 10^{-38}}{6.68 \times 10^{-27}} \approx 2.1557 \times 10^{-12}\text{ J}$। $\text{MeV}$-তে: $E_k = \frac{2.1557 \times 10^{-12}}{1.6 \times 10^{-13}} \approx 13.47\text{ MeV}$।</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 41</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
+          <t>সর্বোচ্চ গতিশক্তি $E_{\max} = 13.47\text{ MeV}$</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5799,12 +5505,12 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ (সমস্যা 42)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -5812,31 +5518,25 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##
-[সমস্যা 42: স্টেপ-ডাউন ট্রান্সফরমার ও ক্ষমতা সংরক্ষণ]
-##PRESET:transformer[size:medium]##
-একটি আদর্শ ট্রান্সফরমারের মুখ্য কুণ্ডলীর পাকসংখ্যা $N_p = 200$ এবং গৌণ কুণ্ডলীর পাকসংখ্যা $N_s = 50$। মুখ্য কুণ্ডলীতে $220\text{ V}$ ভোল্টেজ প্রয়োগ করলে গৌণ কুণ্ডলীর প্রান্তীয় ভোল্টেজ এবং মুখ্য প্রবাহ $1\text{ A}$ হলে গৌণ প্রবাহ কত?</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি সমান্তরাল পাত ধারককে একটি এসি ভোল্টেজ দ্বারা চার্জ করা হচ্ছে। ম্যাক্সওয়েলের সরণ প্রবাহের (Displacement Current) ধারণাটি ব্যাখ্যা কর এবং দেখাও যে পাতের মধ্যবর্তী শূন্যস্থানে সরণ প্রবাহ পরিবাহী তারের কারেন্টের সমান।</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>##PRESET:transformer[size:medium]##</t>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 42)।</t>
+          <t>ধারকের দুই পাতের মাঝে কোনো মুক্ত ইলেকট্রন না থাকলেও পরিবর্তনশীল তড়িৎ ক্ষেত্র সৃষ্টি হয়। ম্যাক্সওয়েল প্রস্তাব করেন পরিবর্তনশীল তড়িৎ ফ্লাক্সের পরিবর্তনের হার একটি কার্যকর কারেন্টের ন্যায় আচরণ করে: $I_d = \epsilon_0 \frac{d}{dt}(E A) = \epsilon_0 A \frac{d}{dt}\left(\frac{q}{\epsilon_0 A}\right) = \frac{dq}{dt} = I_c$। এর ফলে অ্যাম্পিয়ারের সংশোধিত সূত্র অবিচ্ছিন্নতা রক্ষা করে।</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 42</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
+          <t>সরণ প্রবাহ $I_d = \epsilon_0 \frac{d\Phi_E}{dt} = I_c$ (পরিবাহী প্রবাহের সমান)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5856,38 +5556,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল (সমস্যা 43)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>[সমস্যা 43: ফ্যারাডের সূত্র ও আবিষ্ট তড়িচ্চালক বল]
-একটি $N = 400$ পাকের কুণ্ডলীর মধ্য দিয়ে চৌম্বক ফ্লাক্স $\Delta t = 0.7\text{ s}$-এ $0.08\text{ Wb}$ হতে $0.02\text{ Wb}$-এ হ্রাস পেল। কুণ্ডলীতে আবিষ্ট গড় তড়িচ্চালক বল ($e = -N\frac{\Delta\Phi}{\Delta t}$) কত ভোল্ট?</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি $LCR$ সমান্তরাল বর্তনীতে কোন শর্তে অনুনাদ সৃষ্টি হয় এবং সমান্তরাল অনুনাদে বর্তনীর প্রতিবন্ধকতা ও প্রবাহের বৈশিষ্ট্য কী?</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 43)।</t>
+          <t>ব্যবহারিক সমান্তরাল কুণ্ডলী ($R-L$ শাখা ও $C$ শাখা) থাকলে অনুনাদী কম্পাঙ্ক $\omega_0 = \sqrt{\frac{1}{LC} - \frac{R^2}{L^2}}$। অনুনাদ অবস্থায় বর্তনীর সমতুল্য গতিশীল প্রতিবন্ধকতা (Dynamic impedance) $Z = \frac{L}{C R}$ সর্বোচ্চ হয়, যার ফলে প্রধান লাইনের কারেন্ট সর্বনিম্ন মানে নেমে আসে।</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 43</t>
-        </is>
-      </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
-      <c r="N94" t="inlineStr"/>
+          <t>অনুনাদে প্রতিবন্ধকতা সর্বোচ্চ ($Z_{\max} = \frac{L}{C R}$), প্রবাহ সর্বনিম্ন</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5907,12 +5607,12 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ (সমস্যা 44)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -5920,25 +5620,25 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>[সমস্যা 44: ঘূর্ণনশীল পরিবাহী দণ্ডের গতিশীল ইএমএফ]
-$L = 1.0\text{ m}$ দীর্ঘ একটি ধাতব পরিবাহী দণ্ড $B = 0.6\text{ T}$ সুষম চৌম্বক ক্ষেত্রের সাথে লম্বভাবে এক প্রান্তকে কেন্দ্র করে $\omega = 90\text{ rad/s}$ কৌণিক দ্রুতিতে ঘুরছে। দণ্ডের দুই প্রান্তের মধ্যে আবিষ্ট বিভব পার্থক্য ($e = \frac{1}{2}B\omega L^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+একটি আয়তাকার কুণ্ডলী $N = 50$ পাকের, দৈর্ঘ্য $20\text{ cm}$ ও প্রস্থ $10\text{ cm}$। এটি $B = 0.50\text{ T}$ চৌম্বক ক্ষেত্রে প্রতি মিনিটে $1800\text{ বার}$ ঘোরে। কুণ্ডলীতে আবিষ্ট সর্বোচ্চ তড়িচ্চালক বল কত?</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 44)।</t>
+          <t>ক্ষেত্রফল $A = 0.20 \times 0.10 = 0.020\text{ m}^2$। ঘূর্ণন কম্পাঙ্ক $f = \frac{1800}{60} = 30.0\text{ Hz}$। কৌণিক দ্রুতি $\omega = 2\pi f = 2\pi(30) = 60\pi \approx 188.5\text{ rad/s}$। শীর্ষ $\text{EMF} \mathcal{E}_0 = N B A \omega = 50 \times 0.50 \times 0.020 \times 60\pi = 0.50 \times 60\pi = 30\pi \approx 94.248\text{ V}$।</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 44</t>
-        </is>
-      </c>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
+          <t>সর্বোচ্চ $\text{EMF} \mathcal{E}_0 = 94.25\text{ V}$</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5958,38 +5658,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি (সমস্যা 45)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F96" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>[সমস্যা 45: স্বকীয় আবেশাঙ্ক ও সঞ্চিত চৌম্বক শক্তি]
-একটি কুণ্ডলীর স্বকীয় আবেশাঙ্ক $L = 8.0\text{ H}$। এর মধ্য দিয়ে বিদ্যুৎ প্রবাহ $0.1\text{ s}$ সময়ে $1\text{ A}$ হতে শূন্যে নেমে এলে আবিষ্ট ইএমএফ এবং প্রাথমিক অবস্থায় সঞ্চিত শক্তি ($U = \frac{1}{2}LI^2$) কত?</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=3][size:small]##
+একটি ট্রান্সফরমারের মুখ্য কুণ্ডলীতে $V_p = 220\text{ V}$ এবং কারেন্ট $I_p = 5.0\text{ A}$। গৌণ কুণ্ডলীতে $V_s = 2200\text{ V}$ এবং কারেন্ট $I_s = 0.45\text{ A}$ হলে ট্রান্সফরমারটির দক্ষতা $\eta$ কত?</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 45)।</t>
+          <t>ইনপুট ক্ষমতা $P_{\text{in}} = V_p I_p = 220 \times 5.0 = 1100.0\text{ W}$। আউটপুট ক্ষমতা $P_{\text{out}} = V_s I_s = 2200 \times 0.45 = 990.0\text{ W}$। দক্ষতা $\eta = \frac{P_{\text{out}}}{P_{\text{in}}} \times 100\% = \frac{990}{1100} \times 100\% = 0.90 \times 100\% = 90.0\%$।</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 45</t>
-        </is>
-      </c>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
+          <t>কর্মদক্ষতা $\eta = 90.0\%$</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6009,12 +5709,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ (সমস্যা 46)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -6022,25 +5722,25 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>[সমস্যা 46: পারস্পরিক আবেশ গুণাঙ্ক ও আবিষ্ট ভোল্টেজ]
-দুটি পাশাপাশি রাখা কুণ্ডলীর পারস্পরিক আবেশ গুণাঙ্ক $M = 0.10\text{ H}$। মুখ্য কুণ্ডলীতে প্রবাহ $\Delta t = 0.05\text{ s}$-এ শূন্য হতে $3\text{ A}$-তে উন্নীত করলে গৌণ কুণ্ডলীতে আবিষ্ট ইএমএফ কত?</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি ধাতব গোলককে একটি পরিবর্তনশীল চৌম্বক ক্ষেত্রে রাখলে গোলকটিতে কী ঘটবে এবং কেন ধাতুটি দ্রুত উত্তপ্ত হয়ে ওঠে?</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 46)।</t>
+          <t>পরিবর্তনশীল চৌম্বক ক্ষেত্রে ধাতব গোলকটির প্রতিটি স্তর ফ্যারাডের আবেশ নীতি অনুভব করে। ধাতুর রোধ অত্যন্ত কম হওয়ায় বিশাল মানের ঘূর্ণি প্রবাহ আবিষ্ট হয়, যা ধাতুটির অভ্যন্তরীণ রোধে $I^2 R$ হারে তাপ শক্তি উৎপন্ন করে। এই নীতি ব্যবহার করেই আধুনিক ইনডাকশন ফার্নেসে লোহা গলানো হয়।</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 46</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+          <t>ধাতুর অভ্যন্তরে শক্তিশালী ঘূর্ণি প্রবাহ (Eddy currents) আবিষ্ট হয়ে জুলের তাপে উত্তপ্ত হয়</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6060,38 +5760,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান (সমস্যা 47)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>[সমস্যা 47: পরিবর্তী ভোল্টেজের আরএমএস ও শীর্ষ মান]
-একটি সাইনুসয়েডাল পরিবর্তী ভোল্টেজের সমীকরণ $V(t) = 1200 \sin(500\pi t)\text{ V}$। উৎসটির শীর্ষ ভোল্টেজ ($V_0$), কার্যকর ভোল্টেজ ($V_{rms}$) এবং কম্পাঙ্ক ($f$) নির্ণয় কর।</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি $100\text{ W}$ বাতি $220\text{ V}, 50\text{ Hz}$ এসি মেইন্সে চলে। বাতির সাথে শ্রেণিতে কত আবেশাঙ্কের চোক কয়েল যুক্ত করলে বাতিটি $110\text{ V}$ উৎসে একই উজ্জ্বলতায় জ্বলবে?</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 47)।</t>
+          <t>বাতির স্বাভাবিক রোধ $R = \frac{V^2}{P} = \frac{110^2}{100} = 121\text{ }\Omega$ (যদি এটি $110\text{ V}$-এর বাতি হয়)। $220\text{ V}$ লাইনে একই কারেন্ট ($I = 100/110 = 0.909\text{ A}$) পেতে প্রয়োজনীয় মোট প্রতিবন্ধকতা $Z = \frac{220}{0.909} = 242\text{ }\Omega$। $Z = \sqrt{R^2 + X_L^2} \implies X_L = \sqrt{242^2 - 121^2} = 121\sqrt{3} \approx 209.58\text{ }\Omega$। আবেশাঙ্ক $L = \frac{X_L}{2\pi f} = \frac{209.58}{314.16} \approx 0.667\text{ H}$।</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 47</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
-      <c r="N98" t="inlineStr"/>
+          <t>চোক কয়েলের আবেশাঙ্ক $L = 1.33\text{ H}$</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6111,12 +5811,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত (সমস্যা 48)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -6124,25 +5824,25 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>[সমস্যা 48: আবেশীয় প্রতিঘাত ও ধারকীয় প্রতিঘাত]
-একটি $L = 0.2\text{ H}$ আবেশকের মধ্য দিয়ে $f = 50\text{ Hz}$ কম্পাঙ্কের পরিবর্তী প্রবাহ চলছে। আবেশকটির আবেশীয় প্রতিঘাত ($X_L = 2\pi f L$) কত ওহম?</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr"/>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##
+একটি এসি মোটরের আউটপুট যান্ত্রিক ক্ষমতা $P_{	ext{out}} = 5.0\text{ HP}$ ($1\text{ HP} = 746\text{ W}$)। মোটরটি $220\text{ V}$ মেইন্সে $80\%$ দক্ষতায় কাজ করে এবং এর ক্ষমতা গুণক $0.85$। মোটরটির গৃহীত লাইন কারেন্ট $I_{	ext{rms}}$ কত?</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>##GEO:cylinder[r=2,h=3][size:small]##</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 48)।</t>
+          <t>আউটপুট ক্ষমতা $P_{\text{out}} = 5 \times 746 = 3730\text{ W}$। ইনপুট বৈদ্যুতিক ক্ষমতা $P_{\text{in}} = \frac{3730}{0.80} = 4662.5\text{ W}$। আবার $P_{\text{in}} = V I \cos\phi \implies I = \frac{P_{\text{in}}}{V \cos\phi} = \frac{4662.5}{220 \times 0.85} = \frac{4662.5}{187.0} \approx 24.933\text{ A}$।</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 48</t>
-        </is>
-      </c>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
+          <t>লাইন কারেন্ট $I_{\text{rms}} = 24.93\text{ A}$</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6162,38 +5862,38 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>বর্তনীর ক্ষমতা গুণক (Power Factor) (সমস্যা 49)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>[সমস্যা 49: বর্তনীর ক্ষমতা গুণক (Power Factor)]
-একটি পরিবর্তী বর্তনীতে রোধ $R = 40\ \Omega$ এবং মোট প্রতিবন্ধকতা $Z = 90\ \Omega$। বর্তনীর ক্ষমতা গুণক ($\\cos\phi = R/Z$) কত এবং $V_{rms} = 220\text{ V}$ হলে ব্যয়িত গড় ক্ষমতা কত ওয়াট?</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr"/>
+          <t>##GEO:circle[r=2.5][size:small]##
+একটি বৃত্তাকার কুণ্ডলী যার ব্যাসার্ধ $R$ এবং রোধ $R_w$, একটি সুষম চৌম্বক ক্ষেত্রে $\omega$ কৌণিক বেগে ঘুরছে। প্রতি ঘূর্ণনে কুণ্ডলীকে ঘোরাতে বাহ্যিক এজেন্ট কর্তৃক কৃত গড় কাজের রাশিমালা প্রতিপাদন কর।</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>##GEO:circle[r=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 49)।</t>
+          <t>গড় ক্ষমতা $P_{\text{avg}} = \frac{\mathcal{E}_0^2}{2 R_w} = \frac{B^2 A^2 \omega^2}{2 R_w}$। একটি পূর্ণ আবর্তনের সময় $T = \frac{2\pi}{\omega}$। প্রতি আবর্তনে কৃতকাজ $W = P_{\text{avg}} \times T = \frac{B^2 A^2 \omega^2}{2 R_w}\left(\frac{2\pi}{\omega}\right) = \frac{\pi B^2 A^2 \omega}{R_w}$।</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 49</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
+          <t>$W_{\text{rev}} = \frac{\pi B^2 A^2 \omega}{R_w}$</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6213,12 +5913,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ (সমস্যা 50)</t>
+          <t>উন্নত তাড়িতচৌম্বক বিশ্লেষণ ও এসি সংশ্লেষণ (Advanced Induction &amp; AC Synthesis)</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>HARD</t>
+          <t>TOUGH</t>
         </is>
       </c>
       <c r="F101" t="n">
@@ -6226,25 +5926,25 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>[সমস্যা 50: ডিসি জেনারেটরের আর্মেচারের সর্বোচ্চ ইএমএফ]
-একটি আয়তাকার কুণ্ডলী $N = 600$ পাক এবং ক্ষেত্রফল $A = 0.01\text{ m}^2$। এটি $B = 0.5\text{ T}$ চৌম্বক ক্ষেত্রে $\omega = 100\pi\text{ rad/s}$ বেগে ঘুরলে সর্বোচ্চ আবিষ্ট ভোল্টেজ ($e_0 = NAB\omega$) কত?</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##
+আবেশক ও ধারকের শক্তির ঘনত্বের মধ্যে প্রতিসাম্য: দেখাও যে তড়িৎ ক্ষেত্রের শক্তি ঘনত্ব $u_E = rac{1}{2}\epsilon_0 E^2$ এবং চৌম্বক ক্ষেত্রের শক্তি ঘনত্ব $u_B = rac{B^2}{2\mu_0}$। একটি তাড়িতচৌম্বক তরঙ্গে এই দুই শক্তি ঘনত্বের অনুপাত কত?</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>##GEO:rect[w=4,h=2.5][size:small]##</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>ফ্যারাডের সূত্র, লেঞ্জের নীতি ও এসি বর্তনীর জটিল প্রতিবন্ধকতার সমীকরণ দ্বারা সমাধান (সমস্যা 50)।</t>
+          <t>তাড়িতচৌম্বক তরঙ্গে $E = c B$ এবং $c = \frac{1}{\sqrt{\mu_0\epsilon_0}}$। তড়িৎ শক্তি ঘনত্ব $u_E = \frac{1}{2}\epsilon_0 E^2 = \frac{1}{2}\epsilon_0 (c B)^2 = \frac{1}{2}\epsilon_0 \left(\frac{1}{\mu_0\epsilon_0}\right) B^2 = \frac{B^2}{2\mu_0} = u_B$। সুতরাং তাড়িতচৌম্বক তরঙ্গে তড়িৎ ও চৌম্বক ক্ষেত্রের শক্তি ঘনত্ব পরস্পরের হুবহু সমান।</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>তাড়িতচৌম্বক আবেশের সমাধান 50</t>
-        </is>
-      </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
+          <t>$u_E = u_B$, অনুপাত $1 : 1$ (উভয় ক্ষেত্রে শক্তি সমভাবে বণ্টিত থাকে)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
